--- a/KABUTECH_HIYAS_MATERIALS_CHECKLIST.xlsx
+++ b/KABUTECH_HIYAS_MATERIALS_CHECKLIST.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="📋 Materials Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="📊 Executive Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="🛒 Vendor &amp; Shopping Guide" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Materials Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 Executive Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🛒 Vendor &amp; Shopping Guide" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1380,7 +1380,7 @@
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>🏠 CATEGORY B: HANGING SENSOR PROBE HOUSING (PVC BELL REDUCER DESIGN)</t>
+          <t>🏠 CATEGORY B: HANGING SENSOR PROBE HOUSING (MINI RADIATION SHIELD DESIGN)</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -1398,7 +1398,7 @@
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
     </row>
-    <row r="15" ht="44" customHeight="1">
+    <row r="15" ht="58" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>To Buy</t>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>2" to 1" PVC Bell Reducer (White/Gray)</t>
+          <t>Mini Multi-Plate Solar Radiation Shield</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Schedule 40 PVC fitting. 2" bell opening down to 1" neck. Lightweight housing.</t>
+          <t>Multi-tier white ABS louvered disc shelter with internal cavity &amp; top cable gland. 360° airflow, sheds mist.</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="H15" s="15" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>45</v>
+        <v>350</v>
       </c>
       <c r="J15" s="16">
         <f>F15*H15</f>
@@ -1449,17 +1449,17 @@
       <c r="L15" s="16" t="n"/>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>Local Hardware (Citi / Wilcon / Ace)</t>
+          <t>Shopee / Lazada</t>
         </is>
       </c>
       <c r="N15" s="17" t="inlineStr">
         <is>
-          <t>2 x 1 PVC bell reducer fitting</t>
+          <t>Mini radiation shield sensor weather station</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>Forms inverted bell chamber shielding sensors from mist.</t>
+          <t>Houses SHT31, SCD41, BH1750. Eliminates DIY PVC pipe cutting/gluing.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>M16 or M20 IP68 Waterproof Cable Gland</t>
+          <t>PTFE Hydrophobic Membrane Disc (13-25mm)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>Nylon PA66 body, rubber clamping ring, IP68 rated, fits cables 4-8mm / 6-12mm.</t>
+          <t>ePTFE breathable membrane, hydrophobic IP67 rating, gas permeable.</t>
         </is>
       </c>
       <c r="F16" s="22" t="n">
@@ -1514,17 +1514,17 @@
       <c r="L16" s="25" t="n"/>
       <c r="M16" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Lazada / Hardware</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="N16" s="26" t="inlineStr">
         <is>
-          <t>M16 or M20 cable gland IP68 waterproof</t>
+          <t>PTFE membrane disc sensor waterproof</t>
         </is>
       </c>
       <c r="O16" s="21" t="inlineStr">
         <is>
-          <t>Screws into top neck; clamps cable and hangs probe.</t>
+          <t>Affixed over SCD41 aperture to prevent condensation fouling.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>PG7 Cable Gland (Nylon, IP68)</t>
+          <t>Nylon Cable Zip Ties (100mm)</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1551,22 +1551,22 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Mini cable gland for 3-6.5mm cables, weatherproof sealing.</t>
+          <t>2.5mm × 100mm black nylon UV-resistant zip ties (Pack of 100).</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J17" s="16">
         <f>F17*H17</f>
@@ -1579,17 +1579,17 @@
       <c r="L17" s="16" t="n"/>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Hardware Store</t>
+          <t>Hardware Store / Shopee</t>
         </is>
       </c>
       <c r="N17" s="17" t="inlineStr">
         <is>
-          <t>PG7 cable gland nylon IP68</t>
+          <t>Nylon zip ties 100mm black pack</t>
         </is>
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Internal cable strain relief and wire pass-throughs.</t>
+          <t>Internal cable strain relief inside shield.</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>Fine Stainless Steel Mesh / Nylon Filter</t>
+          <t>Printed Weatherproof Vinyl Label Sticker</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>80-120 mesh SS304 wire cloth or dense nylon micron mesh.</t>
+          <t>Weatherproof vinyl sticker: 'KABUTECH HIYAS — Probe SN-01'.</t>
         </is>
       </c>
       <c r="F18" s="22" t="n">
@@ -1624,14 +1624,14 @@
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H18" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" s="24" t="n">
         <v>30</v>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>60</v>
       </c>
       <c r="J18" s="25">
         <f>F18*H18</f>
@@ -1644,149 +1644,70 @@
       <c r="L18" s="25" t="n"/>
       <c r="M18" s="21" t="inlineStr">
         <is>
-          <t>Hardware Store / Shopee</t>
+          <t>Print Shop / DIY Vinyl</t>
         </is>
       </c>
       <c r="N18" s="26" t="inlineStr">
         <is>
-          <t>Stainless steel 304 mesh screen 100 mesh</t>
+          <t>Waterproof vinyl sticker printing</t>
         </is>
       </c>
       <c r="O18" s="21" t="inlineStr">
         <is>
-          <t>Glued to 2" bottom rim. Stops droplets, passes CO2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>PTFE Hydrophobic Membrane Disc (13-25mm)</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Hanging Sensor Probe Housing</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>ePTFE breathable membrane, hydrophobic IP67 rating, gas permeable.</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="J19" s="16">
-        <f>F19*H19</f>
-        <v/>
-      </c>
-      <c r="K19" s="16">
-        <f>F19*I19</f>
-        <v/>
-      </c>
-      <c r="L19" s="16" t="n"/>
-      <c r="M19" s="12" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="N19" s="17" t="inlineStr">
-        <is>
-          <t>PTFE membrane disc sensor waterproof</t>
-        </is>
-      </c>
-      <c r="O19" s="12" t="inlineStr">
-        <is>
-          <t>Glued over SCD41 aperture to prevent condensation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>PVC Solvent Cement &amp; Rapid Epoxy</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>Hanging Sensor Probe Housing</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>100ml PVC cement + 2-part rapid epoxy (Pioneer/Devcon).</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>tube</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>45</v>
-      </c>
-      <c r="I20" s="24" t="n">
-        <v>80</v>
-      </c>
-      <c r="J20" s="25">
-        <f>F20*H20</f>
-        <v/>
-      </c>
-      <c r="K20" s="25">
-        <f>F20*I20</f>
-        <v/>
-      </c>
-      <c r="L20" s="25" t="n"/>
-      <c r="M20" s="21" t="inlineStr">
-        <is>
-          <t>Any Hardware Store</t>
-        </is>
-      </c>
-      <c r="N20" s="26" t="inlineStr">
-        <is>
-          <t>PVC cement Neltex + Pioneer epoxy</t>
-        </is>
-      </c>
-      <c r="O20" s="21" t="inlineStr">
-        <is>
-          <t>Bonds screen to PVC rim and seals gland threads.</t>
-        </is>
-      </c>
+          <t>Professional thesis branding for probe assembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Subtotal — Category B (Hanging Sensor Probe Housing):</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="28" t="n"/>
+      <c r="J19" s="29">
+        <f>SUM(J15:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="29">
+        <f>SUM(K15:K18)</f>
+        <v/>
+      </c>
+      <c r="L19" s="29">
+        <f>SUM(L15:L18)</f>
+        <v/>
+      </c>
+      <c r="M19" s="28" t="n"/>
+      <c r="N19" s="28" t="n"/>
+      <c r="O19" s="28" t="n"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>🧠 CATEGORY C: CONTROLLER BOARD &amp; CORE ELECTRONICS</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -1796,22 +1717,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>B7</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Printed Vinyl Label Sticker</t>
+          <t>ESP32-S3 DevKit N16R8 (USB-C)</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Hanging Sensor Probe Housing</t>
+          <t>Controller Board &amp; Core Electronics</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Weatherproof vinyl sticker: 'KABUTECH HIYAS — Probe SN-01'.</t>
+          <t>16MB Flash, 8MB PSRAM, 240MHz Dual Core, WiFi 4 + BLE 5.0. Dual USB-C.</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
@@ -1823,10 +1744,10 @@
         </is>
       </c>
       <c r="H21" s="15" t="n">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="J21" s="16">
         <f>F21*H21</f>
@@ -1839,17 +1760,17 @@
       <c r="L21" s="16" t="n"/>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>Print Shop / DIY Vinyl</t>
+          <t>Shopee / Makerlab PH / Circuit Rocks</t>
         </is>
       </c>
       <c r="N21" s="17" t="inlineStr">
         <is>
-          <t>Waterproof vinyl sticker printing</t>
+          <t>ESP32-S3 N16R8 DevKit USB-C</t>
         </is>
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>Professional thesis branding for probe assembly.</t>
+          <t>Verify 'N16R8' in listing for full memory &amp; speed.</t>
         </is>
       </c>
     </row>
@@ -1861,22 +1782,22 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>B8</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>Nylon Cable Zip Ties (100mm)</t>
+          <t>8-Channel Relay Module (5V, Optocoupled)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Hanging Sensor Probe Housing</t>
+          <t>Controller Board &amp; Core Electronics</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>2.5mm × 100mm black nylon UV-resistant zip ties (Pack of 100).</t>
+          <t>8-ch optoisolated relay board, active LOW trigger, 10A 250VAC rating.</t>
         </is>
       </c>
       <c r="F22" s="22" t="n">
@@ -1884,14 +1805,14 @@
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H22" s="24" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>45</v>
+        <v>280</v>
       </c>
       <c r="J22" s="25">
         <f>F22*H22</f>
@@ -1904,70 +1825,149 @@
       <c r="L22" s="25" t="n"/>
       <c r="M22" s="21" t="inlineStr">
         <is>
-          <t>Hardware Store / Shopee</t>
+          <t>Shopee / Lazada / Makerlab PH</t>
         </is>
       </c>
       <c r="N22" s="26" t="inlineStr">
         <is>
-          <t>Nylon zip ties 100mm black pack</t>
+          <t>8 channel relay module 5V optocoupler</t>
         </is>
       </c>
       <c r="O22" s="21" t="inlineStr">
         <is>
-          <t>Internal wire bundling and strain relief.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>Subtotal — Category B (Hanging Sensor Probe Housing):</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="n"/>
-      <c r="C23" s="28" t="n"/>
-      <c r="D23" s="28" t="n"/>
-      <c r="E23" s="28" t="n"/>
-      <c r="F23" s="28" t="n"/>
-      <c r="G23" s="28" t="n"/>
-      <c r="H23" s="28" t="n"/>
-      <c r="I23" s="28" t="n"/>
-      <c r="J23" s="29">
-        <f>SUM(J15:J22)</f>
-        <v/>
-      </c>
-      <c r="K23" s="29">
-        <f>SUM(K15:K22)</f>
-        <v/>
-      </c>
-      <c r="L23" s="29">
-        <f>SUM(L15:L22)</f>
-        <v/>
-      </c>
-      <c r="M23" s="28" t="n"/>
-      <c r="N23" s="28" t="n"/>
-      <c r="O23" s="28" t="n"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>🧠 CATEGORY C: CONTROLLER BOARD &amp; CORE ELECTRONICS</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
-      <c r="O24" s="8" t="n"/>
+          <t>Controls: Exhaust, Intake, Mister, Light, Solenoid + 3 spares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Logic Level Shifter (3.3V ↔ 5V, 4-Ch)</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Controller Board &amp; Core Electronics</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Bi-directional I2C / digital logic level converter with BSS138 MOSFETs.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J23" s="16">
+        <f>F23*H23</f>
+        <v/>
+      </c>
+      <c r="K23" s="16">
+        <f>F23*I23</f>
+        <v/>
+      </c>
+      <c r="L23" s="16" t="n"/>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>Shopee / Lazada</t>
+        </is>
+      </c>
+      <c r="N23" s="17" t="inlineStr">
+        <is>
+          <t>4 channel logic level converter 3.3V 5V</t>
+        </is>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>Protects ESP32 3.3V GPIOs driving 5V relay inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Mini Breadboard / Expansion Strips</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Controller Board &amp; Core Electronics</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>170-tie point mini solderless breadboard with adhesive backing.</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="J24" s="25">
+        <f>F24*H24</f>
+        <v/>
+      </c>
+      <c r="K24" s="25">
+        <f>F24*I24</f>
+        <v/>
+      </c>
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>Shopee / Electronics Store</t>
+        </is>
+      </c>
+      <c r="N24" s="26" t="inlineStr">
+        <is>
+          <t>170 tie point mini breadboard</t>
+        </is>
+      </c>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>Prototyping power rail distribution inside cabinet.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>ESP32-S3 DevKit N16R8 (USB-C)</t>
+          <t>LM2596 DC-DC Step-Down Buck Converter</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>16MB Flash, 8MB PSRAM, 240MHz Dual Core, WiFi 4 + BLE 5.0. Dual USB-C.</t>
+          <t>Input 4-40V, Output 1.25-35V adjustable, 3A peak, high efficiency.</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="H25" s="15" t="n">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="J25" s="16">
         <f>F25*H25</f>
@@ -2020,17 +2020,17 @@
       <c r="L25" s="16" t="n"/>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Makerlab PH / Circuit Rocks</t>
+          <t>Shopee / Lazada</t>
         </is>
       </c>
       <c r="N25" s="17" t="inlineStr">
         <is>
-          <t>ESP32-S3 N16R8 DevKit USB-C</t>
+          <t>LM2596 DC-DC buck converter module</t>
         </is>
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Verify 'N16R8' in listing for full memory &amp; speed.</t>
+          <t>Steps down 12V rail to clean 5.0V for MCU &amp; relays.</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>8-Channel Relay Module (5V, Optocoupled)</t>
+          <t>5V 1A Voltage Regulator Module (AMS1117)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>8-ch optoisolated relay board, active LOW trigger, 10A 250VAC rating.</t>
+          <t>Linear regulator module with input/output filter capacitors &amp; power LED.</t>
         </is>
       </c>
       <c r="F26" s="22" t="n">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="H26" s="24" t="n">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="J26" s="25">
         <f>F26*H26</f>
@@ -2085,17 +2085,17 @@
       <c r="L26" s="25" t="n"/>
       <c r="M26" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Lazada / Makerlab PH</t>
+          <t>Shopee / Electronics Store</t>
         </is>
       </c>
       <c r="N26" s="26" t="inlineStr">
         <is>
-          <t>8 channel relay module 5V optocoupler</t>
+          <t>AMS1117 5V power supply module</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
         <is>
-          <t>Controls: Exhaust, Intake, Mister, Light, Solenoid + 3 spares.</t>
+          <t>Dedicated filtered 5V rail to prevent relay-induced brownouts.</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Logic Level Shifter (3.3V ↔ 5V, 4-Ch)</t>
+          <t>3-Position Toggle Switch (Auto/Off/Manual)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Bi-directional I2C / digital logic level converter with BSS138 MOSFETs.</t>
+          <t>Panel-mount 3-position (ON-OFF-ON) heavy-duty toggle switch.</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
@@ -2150,17 +2150,17 @@
       <c r="L27" s="16" t="n"/>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Lazada</t>
+          <t>Shopee / Hardware Store</t>
         </is>
       </c>
       <c r="N27" s="17" t="inlineStr">
         <is>
-          <t>4 channel logic level converter 3.3V 5V</t>
+          <t>Toggle switch 3 position ON-OFF-ON panel mount</t>
         </is>
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>Protects ESP32 3.3V GPIOs driving 5V relay inputs.</t>
+          <t>Hardware override switch: Auto PID / Off / Manual Mode.</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>Mini Breadboard / Expansion Strips</t>
+          <t>5mm LEDs (R, G, B, Y) + 220Ω Resistors</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -2187,19 +2187,19 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>170-tie point mini solderless breadboard with adhesive backing.</t>
+          <t>Panel-mount 5mm LEDs with bezels + 1/4W 220Ω current limiting resistors.</t>
         </is>
       </c>
       <c r="F28" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>set</t>
         </is>
       </c>
       <c r="H28" s="24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>40</v>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="N28" s="26" t="inlineStr">
         <is>
-          <t>170 tie point mini breadboard</t>
+          <t>5mm LED with bezel panel mount set</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
         <is>
-          <t>Prototyping power rail distribution inside cabinet.</t>
+          <t>Front panel indicators: Power (G), WiFi (B), Alarm (R), Mode (Y).</t>
         </is>
       </c>
     </row>
@@ -2237,12 +2237,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>LM2596 DC-DC Step-Down Buck Converter</t>
+          <t>Momentary Push Button (12mm, Panel-Mount)</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Input 4-40V, Output 1.25-35V adjustable, 3A peak, high efficiency.</t>
+          <t>Waterproof momentary push button, normally open (NO), flush metal head.</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="H29" s="15" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="J29" s="16">
         <f>F29*H29</f>
@@ -2280,17 +2280,17 @@
       <c r="L29" s="16" t="n"/>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Lazada</t>
+          <t>Shopee / Electronics Store</t>
         </is>
       </c>
       <c r="N29" s="17" t="inlineStr">
         <is>
-          <t>LM2596 DC-DC buck converter module</t>
+          <t>12mm waterproof momentary push button metal</t>
         </is>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Steps down 12V rail to clean 5.0V for MCU &amp; relays.</t>
+          <t>External Cabinet System Reset / WiFi Provision button.</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>5V 1A Voltage Regulator Module (AMS1117)</t>
+          <t>10kΩ 1/4W Resistors (Pack of 20)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>Linear regulator module with input/output filter capacitors &amp; power LED.</t>
+          <t>1% tolerance 1/4W metal film through-hole resistors.</t>
         </is>
       </c>
       <c r="F30" s="22" t="n">
@@ -2325,14 +2325,14 @@
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="H30" s="24" t="n">
         <v>20</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J30" s="25">
         <f>F30*H30</f>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="N30" s="26" t="inlineStr">
         <is>
-          <t>AMS1117 5V power supply module</t>
+          <t>10k ohm 1/4W metal film resistors pack</t>
         </is>
       </c>
       <c r="O30" s="21" t="inlineStr">
         <is>
-          <t>Dedicated filtered 5V rail to prevent relay-induced brownouts.</t>
+          <t>I2C pull-ups, button debouncing, switch logic.</t>
         </is>
       </c>
     </row>
@@ -2367,12 +2367,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>3-Position Toggle Switch (Auto/Off/Manual)</t>
+          <t>1N4007 Rectifier Diodes (Pack of 10)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Panel-mount 3-position (ON-OFF-ON) heavy-duty toggle switch.</t>
+          <t>1000V 1A standard recovery rectifier diode, DO-41 package.</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
@@ -2390,14 +2390,14 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="I31" s="15" t="n">
         <v>30</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>50</v>
       </c>
       <c r="J31" s="16">
         <f>F31*H31</f>
@@ -2410,17 +2410,17 @@
       <c r="L31" s="16" t="n"/>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Hardware Store</t>
+          <t>Shopee / Electronics Store</t>
         </is>
       </c>
       <c r="N31" s="17" t="inlineStr">
         <is>
-          <t>Toggle switch 3 position ON-OFF-ON panel mount</t>
+          <t>1N4007 diode pack 10pcs</t>
         </is>
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>Hardware override switch: Auto PID / Off / Manual Mode.</t>
+          <t>Flyback diode protection across pump, solenoid &amp; fan coils.</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>5mm LEDs (R, G, B, Y) + 220Ω Resistors</t>
+          <t>Inline Blade Fuse Holder (16AWG) + 5A Fuses</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -2447,22 +2447,22 @@
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
-          <t>Panel-mount 5mm LEDs with bezels + 1/4W 220Ω current limiting resistors.</t>
+          <t>Waterproof automotive inline fuse holder + 5A blade fuses (Pack of 5).</t>
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="H32" s="24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J32" s="25">
         <f>F32*H32</f>
@@ -2475,149 +2475,70 @@
       <c r="L32" s="25" t="n"/>
       <c r="M32" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Electronics Store</t>
+          <t>Shopee / Automotive Store</t>
         </is>
       </c>
       <c r="N32" s="26" t="inlineStr">
         <is>
-          <t>5mm LED with bezel panel mount set</t>
+          <t>Inline blade fuse holder waterproof 16AWG</t>
         </is>
       </c>
       <c r="O32" s="21" t="inlineStr">
         <is>
-          <t>Front panel indicators: Power (G), WiFi (B), Alarm (R), Mode (Y).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>Momentary Push Button (12mm, Panel-Mount)</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Controller Board &amp; Core Electronics</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>Waterproof momentary push button, normally open (NO), flush metal head.</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="J33" s="16">
-        <f>F33*H33</f>
-        <v/>
-      </c>
-      <c r="K33" s="16">
-        <f>F33*I33</f>
-        <v/>
-      </c>
-      <c r="L33" s="16" t="n"/>
-      <c r="M33" s="12" t="inlineStr">
-        <is>
-          <t>Shopee / Electronics Store</t>
-        </is>
-      </c>
-      <c r="N33" s="17" t="inlineStr">
-        <is>
-          <t>12mm waterproof momentary push button metal</t>
-        </is>
-      </c>
-      <c r="O33" s="12" t="inlineStr">
-        <is>
-          <t>External Cabinet System Reset / WiFi Provision button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>10kΩ 1/4W Resistors (Pack of 20)</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>Controller Board &amp; Core Electronics</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>1% tolerance 1/4W metal film through-hole resistors.</t>
-        </is>
-      </c>
-      <c r="F34" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="23" t="inlineStr">
-        <is>
-          <t>pack</t>
-        </is>
-      </c>
-      <c r="H34" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>30</v>
-      </c>
-      <c r="J34" s="25">
-        <f>F34*H34</f>
-        <v/>
-      </c>
-      <c r="K34" s="25">
-        <f>F34*I34</f>
-        <v/>
-      </c>
-      <c r="L34" s="25" t="n"/>
-      <c r="M34" s="21" t="inlineStr">
-        <is>
-          <t>Shopee / Electronics Store</t>
-        </is>
-      </c>
-      <c r="N34" s="26" t="inlineStr">
-        <is>
-          <t>10k ohm 1/4W metal film resistors pack</t>
-        </is>
-      </c>
-      <c r="O34" s="21" t="inlineStr">
-        <is>
-          <t>I2C pull-ups, button debouncing, switch logic.</t>
-        </is>
-      </c>
+          <t>Protects main 12V rail and high-draw actuator branches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>Subtotal — Category C (Controller Board &amp; Core Electronics):</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="28" t="n"/>
+      <c r="J33" s="29">
+        <f>SUM(J21:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="29">
+        <f>SUM(K21:K32)</f>
+        <v/>
+      </c>
+      <c r="L33" s="29">
+        <f>SUM(L21:L32)</f>
+        <v/>
+      </c>
+      <c r="M33" s="28" t="n"/>
+      <c r="N33" s="28" t="n"/>
+      <c r="O33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>⚡ CATEGORY D: POWER SUPPLY &amp; DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
+      <c r="O34" s="8" t="n"/>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
@@ -2627,22 +2548,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>1N4007 Rectifier Diodes (Pack of 10)</t>
+          <t>12V 10A (120W) Enclosed Switching PSU</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Controller Board &amp; Core Electronics</t>
+          <t>Power Supply &amp; Distribution</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>1000V 1A standard recovery rectifier diode, DO-41 package.</t>
+          <t>Metal mesh chassis, universal AC in (110-240V), regulated 12VDC ±1%.</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
@@ -2650,14 +2571,14 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>15</v>
+        <v>450</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>30</v>
+        <v>850</v>
       </c>
       <c r="J35" s="16">
         <f>F35*H35</f>
@@ -2670,17 +2591,17 @@
       <c r="L35" s="16" t="n"/>
       <c r="M35" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Electronics Store</t>
+          <t>Shopee / Lazada / Alexan</t>
         </is>
       </c>
       <c r="N35" s="17" t="inlineStr">
         <is>
-          <t>1N4007 diode pack 10pcs</t>
+          <t>12V 10A switching power supply metal case 120W</t>
         </is>
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Flyback diode protection across pump, solenoid &amp; fan coils.</t>
+          <t>Powers entire system safely with heavy-duty headroom: ESP32, fans, pump, valve.</t>
         </is>
       </c>
     </row>
@@ -2692,37 +2613,37 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>Inline Blade Fuse Holder (16AWG) + 5A Fuses</t>
+          <t>IEC C14 Inlet Socket with Fuse &amp; Switch</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Controller Board &amp; Core Electronics</t>
+          <t>Power Supply &amp; Distribution</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>Waterproof automotive inline fuse holder + 5A blade fuses (Pack of 5).</t>
+          <t>Panel-mount AC socket with built-in 5x20mm fuse drawer &amp; illuminated switch.</t>
         </is>
       </c>
       <c r="F36" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H36" s="24" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I36" s="24" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J36" s="25">
         <f>F36*H36</f>
@@ -2735,70 +2656,149 @@
       <c r="L36" s="25" t="n"/>
       <c r="M36" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Automotive Store</t>
+          <t>Shopee / Lazada / Alexan</t>
         </is>
       </c>
       <c r="N36" s="26" t="inlineStr">
         <is>
-          <t>Inline blade fuse holder waterproof 16AWG</t>
+          <t>IEC C14 power socket with fuse switch panel mount</t>
         </is>
       </c>
       <c r="O36" s="21" t="inlineStr">
         <is>
-          <t>Protects main 12V rail and high-draw actuator branches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t>Subtotal — Category C (Controller Board &amp; Core Electronics):</t>
-        </is>
-      </c>
-      <c r="B37" s="28" t="n"/>
-      <c r="C37" s="28" t="n"/>
-      <c r="D37" s="28" t="n"/>
-      <c r="E37" s="28" t="n"/>
-      <c r="F37" s="28" t="n"/>
-      <c r="G37" s="28" t="n"/>
-      <c r="H37" s="28" t="n"/>
-      <c r="I37" s="28" t="n"/>
-      <c r="J37" s="29">
-        <f>SUM(J25:J36)</f>
-        <v/>
-      </c>
-      <c r="K37" s="29">
-        <f>SUM(K25:K36)</f>
-        <v/>
-      </c>
-      <c r="L37" s="29">
-        <f>SUM(L25:L36)</f>
-        <v/>
-      </c>
-      <c r="M37" s="28" t="n"/>
-      <c r="N37" s="28" t="n"/>
-      <c r="O37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>⚡ CATEGORY D: POWER SUPPLY &amp; DISTRIBUTION</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-      <c r="L38" s="8" t="n"/>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="8" t="n"/>
-      <c r="O38" s="8" t="n"/>
+          <t>Professional computer kettle cord inlet on enclosure face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>220V AC Power Cord (3-Prong PH, 1.5m)</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Power Supply &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Heavy-duty 3-conductor (G, N, L) cable, rated 250V 10A, molded C13 plug.</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="J37" s="16">
+        <f>F37*H37</f>
+        <v/>
+      </c>
+      <c r="K37" s="16">
+        <f>F37*I37</f>
+        <v/>
+      </c>
+      <c r="L37" s="16" t="n"/>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>Hardware Store / Shopee</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>PC power cord 3 prong IEC C13 1.5m</t>
+        </is>
+      </c>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>Standard wall plug with true safety earth grounding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>12-Position Terminal Block Strip (15A)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>Power Supply &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>Dual-row screw terminal strip with clear cover, 15A 600V rated.</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J38" s="25">
+        <f>F38*H38</f>
+        <v/>
+      </c>
+      <c r="K38" s="25">
+        <f>F38*I38</f>
+        <v/>
+      </c>
+      <c r="L38" s="25" t="n"/>
+      <c r="M38" s="21" t="inlineStr">
+        <is>
+          <t>Shopee / Hardware Store</t>
+        </is>
+      </c>
+      <c r="N38" s="26" t="inlineStr">
+        <is>
+          <t>TB-1512 barrier terminal block 12 position 15A</t>
+        </is>
+      </c>
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t>Organized 12V (+), GND (-), and relay output distribution.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>12V 5A (60W) Enclosed Switching PSU</t>
+          <t>Wago 221 Lever Connectors (3-Wire, 5-Pack)</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Metal mesh chassis, universal AC in (110-240V), regulated 12VDC ±1%.</t>
+          <t>Tool-free lever wire connectors, supports 24-12 AWG solid &amp; stranded.</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="J39" s="16">
         <f>F39*H39</f>
@@ -2851,17 +2851,17 @@
       <c r="L39" s="16" t="n"/>
       <c r="M39" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Lazada / Alexan</t>
+          <t>Shopee / Lazada</t>
         </is>
       </c>
       <c r="N39" s="17" t="inlineStr">
         <is>
-          <t>12V 5A switching power supply metal case</t>
+          <t>Wago 221-413 3 wire lever connector</t>
         </is>
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>Powers entire system safely: ESP32, fans, pump, valve.</t>
+          <t>Safe, reusable vibration-proof wire splicing inside box.</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>IEC C14 Inlet Socket with Fuse &amp; Switch</t>
+          <t>KCD1 Rocker Switch (ON-OFF, 220V 6A)</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>Panel-mount AC socket with built-in 5x20mm fuse drawer &amp; illuminated switch.</t>
+          <t>Snap-in SPST rocker switch with red neon indicator, 19×13mm cutout.</t>
         </is>
       </c>
       <c r="F40" s="22" t="n">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="H40" s="24" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J40" s="25">
         <f>F40*H40</f>
@@ -2916,17 +2916,17 @@
       <c r="L40" s="25" t="n"/>
       <c r="M40" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Lazada / Alexan</t>
+          <t>Shopee / Hardware Store</t>
         </is>
       </c>
       <c r="N40" s="26" t="inlineStr">
         <is>
-          <t>IEC C14 power socket with fuse switch panel mount</t>
+          <t>KCD1 rocker switch illuminated red 3 pin</t>
         </is>
       </c>
       <c r="O40" s="21" t="inlineStr">
         <is>
-          <t>Professional computer kettle cord inlet on enclosure face.</t>
+          <t>Master power switch on controller enclosure exterior.</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>220V AC Power Cord (3-Prong PH, 1.5m)</t>
+          <t>Metal Oxide Varistor MOV (275V, 10D431K)</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Heavy-duty 3-conductor (G, N, L) cable, rated 250V 10A, molded C13 plug.</t>
+          <t>275VAC RMS surge suppressor, absorbs grid spikes &amp; brownout transients.</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="H41" s="15" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="J41" s="16">
         <f>F41*H41</f>
@@ -2981,330 +2981,330 @@
       <c r="L41" s="16" t="n"/>
       <c r="M41" s="12" t="inlineStr">
         <is>
-          <t>Hardware Store / Shopee</t>
+          <t>Shopee / Electronics Store</t>
         </is>
       </c>
       <c r="N41" s="17" t="inlineStr">
         <is>
-          <t>PC power cord 3 prong IEC C13 1.5m</t>
+          <t>Varistor 10D431K 275V surge protector</t>
         </is>
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>Standard wall plug with true safety earth grounding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="18" t="inlineStr">
+          <t>Wired across AC Live &amp; Neutral at inlet for surge protection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>Subtotal — Category D (Power Supply &amp; Distribution):</t>
+        </is>
+      </c>
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="28" t="n"/>
+      <c r="J42" s="29">
+        <f>SUM(J35:J41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="29">
+        <f>SUM(K35:K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="29">
+        <f>SUM(L35:L41)</f>
+        <v/>
+      </c>
+      <c r="M42" s="28" t="n"/>
+      <c r="N42" s="28" t="n"/>
+      <c r="O42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>🔌 CATEGORY E: CONNECTORS &amp; WIRING</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="8" t="n"/>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>To Buy</t>
         </is>
       </c>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>12-Position Terminal Block Strip (15A)</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="inlineStr">
-        <is>
-          <t>Power Supply &amp; Distribution</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>Dual-row screw terminal strip with clear cover, 15A 600V rated.</t>
-        </is>
-      </c>
-      <c r="F42" s="22" t="n">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>GX16 4-Pin Aviation Connectors (M+F Sets)</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Connectors &amp; Wiring</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>16mm metal chassis socket + cable plug, screw-locking, 5A rated.</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>sets</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" s="16">
+        <f>F44*H44</f>
+        <v/>
+      </c>
+      <c r="K44" s="16">
+        <f>F44*I44</f>
+        <v/>
+      </c>
+      <c r="L44" s="16" t="n"/>
+      <c r="M44" s="12" t="inlineStr">
+        <is>
+          <t>Shopee / Lazada</t>
+        </is>
+      </c>
+      <c r="N44" s="17" t="inlineStr">
+        <is>
+          <t>GX16 4 pin aviation connector male female</t>
+        </is>
+      </c>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>Detachable ports: Exhaust, Intake, Mister, Light, Probe, Flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>4-Core Shielded Cable (22AWG, 3 Meters)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>Connectors &amp; Wiring</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>4 stranded copper cores + aluminum foil shield + drain wire, flexible PVC.</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>roll (3m)</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="J45" s="25">
+        <f>F45*H45</f>
+        <v/>
+      </c>
+      <c r="K45" s="25">
+        <f>F45*I45</f>
+        <v/>
+      </c>
+      <c r="L45" s="25" t="n"/>
+      <c r="M45" s="21" t="inlineStr">
+        <is>
+          <t>Shopee / Lazada</t>
+        </is>
+      </c>
+      <c r="N45" s="26" t="inlineStr">
+        <is>
+          <t>4 core shielded cable 22AWG signal wire</t>
+        </is>
+      </c>
+      <c r="O45" s="21" t="inlineStr">
+        <is>
+          <t>Controller to probe umbilical. Shielding stops I2C noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>18 AWG Silicone Stranded Wire (Red + Black)</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>Connectors &amp; Wiring</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>High-temp (200°C) flexible tinned copper silicone wire (5m red, 5m black).</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="23" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="H42" s="24" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="24" t="n">
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>rolls</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="I46" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="J42" s="25">
-        <f>F42*H42</f>
-        <v/>
-      </c>
-      <c r="K42" s="25">
-        <f>F42*I42</f>
-        <v/>
-      </c>
-      <c r="L42" s="25" t="n"/>
-      <c r="M42" s="21" t="inlineStr">
-        <is>
-          <t>Shopee / Hardware Store</t>
-        </is>
-      </c>
-      <c r="N42" s="26" t="inlineStr">
-        <is>
-          <t>TB-1512 barrier terminal block 12 position 15A</t>
-        </is>
-      </c>
-      <c r="O42" s="21" t="inlineStr">
-        <is>
-          <t>Organized 12V (+), GND (-), and relay output distribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="J46" s="16">
+        <f>F46*H46</f>
+        <v/>
+      </c>
+      <c r="K46" s="16">
+        <f>F46*I46</f>
+        <v/>
+      </c>
+      <c r="L46" s="16" t="n"/>
+      <c r="M46" s="12" t="inlineStr">
+        <is>
+          <t>Shopee / Lazada</t>
+        </is>
+      </c>
+      <c r="N46" s="17" t="inlineStr">
+        <is>
+          <t>18 AWG silicone wire red black 5m</t>
+        </is>
+      </c>
+      <c r="O46" s="12" t="inlineStr">
+        <is>
+          <t>Main 12V high-current distribution inside cabinet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="44" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>To Buy</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Wago 221 Lever Connectors (3-Wire, 5-Pack)</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>Power Supply &amp; Distribution</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Tool-free lever wire connectors, supports 24-12 AWG solid &amp; stranded.</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="J43" s="16">
-        <f>F43*H43</f>
-        <v/>
-      </c>
-      <c r="K43" s="16">
-        <f>F43*I43</f>
-        <v/>
-      </c>
-      <c r="L43" s="16" t="n"/>
-      <c r="M43" s="12" t="inlineStr">
-        <is>
-          <t>Shopee / Lazada</t>
-        </is>
-      </c>
-      <c r="N43" s="17" t="inlineStr">
-        <is>
-          <t>Wago 221-413 3 wire lever connector</t>
-        </is>
-      </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>Safe, reusable vibration-proof wire splicing inside box.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="44" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>KCD1 Rocker Switch (ON-OFF, 220V 6A)</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>Power Supply &amp; Distribution</t>
-        </is>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>Snap-in SPST rocker switch with red neon indicator, 19×13mm cutout.</t>
-        </is>
-      </c>
-      <c r="F44" s="22" t="n">
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>22 AWG Hookup Wire Assorted (6 Colors, 5m)</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>Connectors &amp; Wiring</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>PVC insulated tinned copper wire in 6 distinct colors.</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="23" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="H44" s="24" t="n">
-        <v>25</v>
-      </c>
-      <c r="I44" s="24" t="n">
-        <v>40</v>
-      </c>
-      <c r="J44" s="25">
-        <f>F44*H44</f>
-        <v/>
-      </c>
-      <c r="K44" s="25">
-        <f>F44*I44</f>
-        <v/>
-      </c>
-      <c r="L44" s="25" t="n"/>
-      <c r="M44" s="21" t="inlineStr">
-        <is>
-          <t>Shopee / Hardware Store</t>
-        </is>
-      </c>
-      <c r="N44" s="26" t="inlineStr">
-        <is>
-          <t>KCD1 rocker switch illuminated red 3 pin</t>
-        </is>
-      </c>
-      <c r="O44" s="21" t="inlineStr">
-        <is>
-          <t>Master power switch on controller enclosure exterior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="44" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>D7</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>Metal Oxide Varistor MOV (275V, 10D431K)</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>Power Supply &amp; Distribution</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>275VAC RMS surge suppressor, absorbs grid spikes &amp; brownout transients.</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="J45" s="16">
-        <f>F45*H45</f>
-        <v/>
-      </c>
-      <c r="K45" s="16">
-        <f>F45*I45</f>
-        <v/>
-      </c>
-      <c r="L45" s="16" t="n"/>
-      <c r="M45" s="12" t="inlineStr">
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J47" s="25">
+        <f>F47*H47</f>
+        <v/>
+      </c>
+      <c r="K47" s="25">
+        <f>F47*I47</f>
+        <v/>
+      </c>
+      <c r="L47" s="25" t="n"/>
+      <c r="M47" s="21" t="inlineStr">
         <is>
           <t>Shopee / Electronics Store</t>
         </is>
       </c>
-      <c r="N45" s="17" t="inlineStr">
-        <is>
-          <t>Varistor 10D431K 275V surge protector</t>
-        </is>
-      </c>
-      <c r="O45" s="12" t="inlineStr">
-        <is>
-          <t>Wired across AC Live &amp; Neutral at inlet for surge protection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="27" t="inlineStr">
-        <is>
-          <t>Subtotal — Category D (Power Supply &amp; Distribution):</t>
-        </is>
-      </c>
-      <c r="B46" s="28" t="n"/>
-      <c r="C46" s="28" t="n"/>
-      <c r="D46" s="28" t="n"/>
-      <c r="E46" s="28" t="n"/>
-      <c r="F46" s="28" t="n"/>
-      <c r="G46" s="28" t="n"/>
-      <c r="H46" s="28" t="n"/>
-      <c r="I46" s="28" t="n"/>
-      <c r="J46" s="29">
-        <f>SUM(J39:J45)</f>
-        <v/>
-      </c>
-      <c r="K46" s="29">
-        <f>SUM(K39:K45)</f>
-        <v/>
-      </c>
-      <c r="L46" s="29">
-        <f>SUM(L39:L45)</f>
-        <v/>
-      </c>
-      <c r="M46" s="28" t="n"/>
-      <c r="N46" s="28" t="n"/>
-      <c r="O46" s="28" t="n"/>
-    </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>🔌 CATEGORY E: CONNECTORS &amp; WIRING</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
-      <c r="L47" s="8" t="n"/>
-      <c r="M47" s="8" t="n"/>
-      <c r="N47" s="8" t="n"/>
-      <c r="O47" s="8" t="n"/>
+      <c r="N47" s="26" t="inlineStr">
+        <is>
+          <t>22 AWG hookup wire kit assorted colors</t>
+        </is>
+      </c>
+      <c r="O47" s="21" t="inlineStr">
+        <is>
+          <t>Internal signal wiring: ESP32 to shifters, display, LEDs.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>GX16 4-Pin Aviation Connectors (M+F Sets)</t>
+          <t>Dupont Jumper Wires (40-Pin, 20cm, Assorted)</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -3329,11 +3329,11 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>16mm metal chassis socket + cable plug, screw-locking, 5A rated.</t>
+          <t>Multicolored breadboard jumpers (M-M, M-F, F-F).</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="H48" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="15" t="n">
         <v>50</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>100</v>
       </c>
       <c r="J48" s="16">
         <f>F48*H48</f>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="N48" s="17" t="inlineStr">
         <is>
-          <t>GX16 4 pin aviation connector male female</t>
+          <t>Dupont wire 20cm 40 pin M-M M-F F-F</t>
         </is>
       </c>
       <c r="O48" s="12" t="inlineStr">
         <is>
-          <t>Detachable ports: Exhaust, Intake, Mister, Light, Probe, Flow.</t>
+          <t>Bench prototyping and test jumpers.</t>
         </is>
       </c>
     </row>
@@ -3379,12 +3379,12 @@
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>4-Core Shielded Cable (22AWG, 3 Meters)</t>
+          <t>IP68 Nylon Cable Glands (PG9 / PG11)</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -3394,22 +3394,22 @@
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
-          <t>4 stranded copper cores + aluminum foil shield + drain wire, flexible PVC.</t>
+          <t>Weatherproof cable entry glands with rubber sealing washers &amp; locknuts.</t>
         </is>
       </c>
       <c r="F49" s="22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>roll (3m)</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="H49" s="24" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="J49" s="25">
         <f>F49*H49</f>
@@ -3422,17 +3422,17 @@
       <c r="L49" s="25" t="n"/>
       <c r="M49" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Lazada</t>
+          <t>Shopee / Hardware Store</t>
         </is>
       </c>
       <c r="N49" s="26" t="inlineStr">
         <is>
-          <t>4 core shielded cable 22AWG signal wire</t>
+          <t>PG9 PG11 cable gland IP68 nylon</t>
         </is>
       </c>
       <c r="O49" s="21" t="inlineStr">
         <is>
-          <t>Controller to probe umbilical. Shielding stops I2C noise.</t>
+          <t>Watertight cable pass-throughs into enclosure.</t>
         </is>
       </c>
     </row>
@@ -3444,12 +3444,12 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>18 AWG Silicone Stranded Wire (Red + Black)</t>
+          <t>Heat Shrink Tubing Kit (120+ pcs Assorted)</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -3459,22 +3459,22 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>High-temp (200°C) flexible tinned copper silicone wire (5m red, 5m black).</t>
+          <t>Polyolefin 2:1 shrink tubing in assorted diameters (1.5mm-10mm).</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>rolls</t>
+          <t>kit</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J50" s="16">
         <f>F50*H50</f>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="N50" s="17" t="inlineStr">
         <is>
-          <t>18 AWG silicone wire red black 5m</t>
+          <t>Heat shrink tubing kit assorted sizes</t>
         </is>
       </c>
       <c r="O50" s="12" t="inlineStr">
         <is>
-          <t>Main 12V high-current distribution inside cabinet.</t>
+          <t>Insulates aviation pins, splice joints, and LED legs.</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>22 AWG Hookup Wire Assorted (6 Colors, 5m)</t>
+          <t>JST-XH 2.54mm Connector Kit (2P, 3P, 4P)</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="E51" s="21" t="inlineStr">
         <is>
-          <t>PVC insulated tinned copper wire in 6 distinct colors.</t>
+          <t>Male PCB headers + female crimp housings + pins in organizer box.</t>
         </is>
       </c>
       <c r="F51" s="22" t="n">
@@ -3532,14 +3532,14 @@
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>kit</t>
         </is>
       </c>
       <c r="H51" s="24" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I51" s="24" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J51" s="25">
         <f>F51*H51</f>
@@ -3552,17 +3552,17 @@
       <c r="L51" s="25" t="n"/>
       <c r="M51" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Electronics Store</t>
+          <t>Shopee / Lazada</t>
         </is>
       </c>
       <c r="N51" s="26" t="inlineStr">
         <is>
-          <t>22 AWG hookup wire kit assorted colors</t>
+          <t>JST-XH 2.54mm connector kit with crimp pins</t>
         </is>
       </c>
       <c r="O51" s="21" t="inlineStr">
         <is>
-          <t>Internal signal wiring: ESP32 to shifters, display, LEDs.</t>
+          <t>Modular disconnects for sensors &amp; display modules.</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E9</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Dupont Jumper Wires (40-Pin, 20cm, Assorted)</t>
+          <t>40-Pin 2.54mm Female Header Strips</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -3589,22 +3589,22 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Multicolored breadboard jumpers (M-M, M-F, F-F).</t>
+          <t>Gold-plated through-hole female socket strips.</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>sets</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J52" s="16">
         <f>F52*H52</f>
@@ -3617,17 +3617,17 @@
       <c r="L52" s="16" t="n"/>
       <c r="M52" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Lazada</t>
+          <t>Shopee / Electronics Store</t>
         </is>
       </c>
       <c r="N52" s="17" t="inlineStr">
         <is>
-          <t>Dupont wire 20cm 40 pin M-M M-F F-F</t>
+          <t>40 pin 2.54mm female header socket strip</t>
         </is>
       </c>
       <c r="O52" s="12" t="inlineStr">
         <is>
-          <t>Bench prototyping and test jumpers.</t>
+          <t>Sockets for ESP32 DevKit so MCU is pluggable/swappable.</t>
         </is>
       </c>
     </row>
@@ -3639,12 +3639,12 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t>IP68 Nylon Cable Glands (PG9 / PG11)</t>
+          <t>Rosin Core Solder Wire (60/40, 0.8mm, 50g)</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -3654,22 +3654,22 @@
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>Weatherproof cable entry glands with rubber sealing washers &amp; locknuts.</t>
+          <t>High purity 60% tin / 40% lead with 2.2% rosin flux core.</t>
         </is>
       </c>
       <c r="F53" s="22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="H53" s="24" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="I53" s="24" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="J53" s="25">
         <f>F53*H53</f>
@@ -3687,144 +3687,65 @@
       </c>
       <c r="N53" s="26" t="inlineStr">
         <is>
-          <t>PG9 PG11 cable gland IP68 nylon</t>
+          <t>Solder wire 60/40 0.8mm rosin core 50g</t>
         </is>
       </c>
       <c r="O53" s="21" t="inlineStr">
         <is>
-          <t>Watertight cable pass-throughs into enclosure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="44" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>E7</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>Heat Shrink Tubing Kit (120+ pcs Assorted)</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>Connectors &amp; Wiring</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>Polyolefin 2:1 shrink tubing in assorted diameters (1.5mm-10mm).</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>kit</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="J54" s="16">
-        <f>F54*H54</f>
-        <v/>
-      </c>
-      <c r="K54" s="16">
-        <f>F54*I54</f>
-        <v/>
-      </c>
-      <c r="L54" s="16" t="n"/>
-      <c r="M54" s="12" t="inlineStr">
-        <is>
-          <t>Shopee / Lazada</t>
-        </is>
-      </c>
-      <c r="N54" s="17" t="inlineStr">
-        <is>
-          <t>Heat shrink tubing kit assorted sizes</t>
-        </is>
-      </c>
-      <c r="O54" s="12" t="inlineStr">
-        <is>
-          <t>Insulates aviation pins, splice joints, and LED legs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="44" customHeight="1">
-      <c r="A55" s="18" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B55" s="18" t="inlineStr">
-        <is>
-          <t>E8</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>JST-XH 2.54mm Connector Kit (2P, 3P, 4P)</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="inlineStr">
-        <is>
-          <t>Connectors &amp; Wiring</t>
-        </is>
-      </c>
-      <c r="E55" s="21" t="inlineStr">
-        <is>
-          <t>Male PCB headers + female crimp housings + pins in organizer box.</t>
-        </is>
-      </c>
-      <c r="F55" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="23" t="inlineStr">
-        <is>
-          <t>kit</t>
-        </is>
-      </c>
-      <c r="H55" s="24" t="n">
-        <v>50</v>
-      </c>
-      <c r="I55" s="24" t="n">
-        <v>80</v>
-      </c>
-      <c r="J55" s="25">
-        <f>F55*H55</f>
-        <v/>
-      </c>
-      <c r="K55" s="25">
-        <f>F55*I55</f>
-        <v/>
-      </c>
-      <c r="L55" s="25" t="n"/>
-      <c r="M55" s="21" t="inlineStr">
-        <is>
-          <t>Shopee / Lazada</t>
-        </is>
-      </c>
-      <c r="N55" s="26" t="inlineStr">
-        <is>
-          <t>JST-XH 2.54mm connector kit with crimp pins</t>
-        </is>
-      </c>
-      <c r="O55" s="21" t="inlineStr">
-        <is>
-          <t>Modular disconnects for sensors &amp; display modules.</t>
-        </is>
-      </c>
+          <t>Permanent soldering of boards, diodes, and aviation plugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>Subtotal — Category E (Connectors &amp; Wiring):</t>
+        </is>
+      </c>
+      <c r="B54" s="28" t="n"/>
+      <c r="C54" s="28" t="n"/>
+      <c r="D54" s="28" t="n"/>
+      <c r="E54" s="28" t="n"/>
+      <c r="F54" s="28" t="n"/>
+      <c r="G54" s="28" t="n"/>
+      <c r="H54" s="28" t="n"/>
+      <c r="I54" s="28" t="n"/>
+      <c r="J54" s="29">
+        <f>SUM(J44:J53)</f>
+        <v/>
+      </c>
+      <c r="K54" s="29">
+        <f>SUM(K44:K53)</f>
+        <v/>
+      </c>
+      <c r="L54" s="29">
+        <f>SUM(L44:L53)</f>
+        <v/>
+      </c>
+      <c r="M54" s="28" t="n"/>
+      <c r="N54" s="28" t="n"/>
+      <c r="O54" s="28" t="n"/>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>🌀 CATEGORY F: ACTUATORS (THE THINGS BEING CONTROLLED)</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
+      <c r="M55" s="8" t="n"/>
+      <c r="N55" s="8" t="n"/>
+      <c r="O55" s="8" t="n"/>
     </row>
     <row r="56" ht="44" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
@@ -3834,37 +3755,37 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>40-Pin 2.54mm Female Header Strips</t>
+          <t>12V DC Exhaust Fan (120mm / 4-Inch)</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Connectors &amp; Wiring</t>
+          <t>Actuators</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Gold-plated through-hole female socket strips.</t>
+          <t>120×120×25mm, 12V DC, ball bearing, moisture-resistant, &gt;70 CFM.</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="J56" s="16">
         <f>F56*H56</f>
@@ -3877,17 +3798,17 @@
       <c r="L56" s="16" t="n"/>
       <c r="M56" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Electronics Store</t>
+          <t>Shopee / Lazada</t>
         </is>
       </c>
       <c r="N56" s="17" t="inlineStr">
         <is>
-          <t>40 pin 2.54mm female header socket strip</t>
+          <t>12V 120mm cooling fan ball bearing high airflow</t>
         </is>
       </c>
       <c r="O56" s="12" t="inlineStr">
         <is>
-          <t>Sockets for ESP32 DevKit so MCU is pluggable/swappable.</t>
+          <t>Extracts stale CO2 and heat from grow room ceiling.</t>
         </is>
       </c>
     </row>
@@ -3899,22 +3820,22 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t>Rosin Core Solder Wire (60/40, 0.8mm, 50g)</t>
+          <t>12V DC Circulation / Intake Fan (80-120mm)</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
         <is>
-          <t>Connectors &amp; Wiring</t>
+          <t>Actuators</t>
         </is>
       </c>
       <c r="E57" s="21" t="inlineStr">
         <is>
-          <t>High purity 60% tin / 40% lead with 2.2% rosin flux core.</t>
+          <t>12V DC, brushless, 0.2A, low noise with finger protection grill.</t>
         </is>
       </c>
       <c r="F57" s="22" t="n">
@@ -3922,14 +3843,14 @@
       </c>
       <c r="G57" s="23" t="inlineStr">
         <is>
-          <t>roll</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H57" s="24" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="I57" s="24" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="J57" s="25">
         <f>F57*H57</f>
@@ -3942,70 +3863,149 @@
       <c r="L57" s="25" t="n"/>
       <c r="M57" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Hardware Store</t>
+          <t>Shopee / Lazada</t>
         </is>
       </c>
       <c r="N57" s="26" t="inlineStr">
         <is>
-          <t>Solder wire 60/40 0.8mm rosin core 50g</t>
+          <t>12V DC brushless fan 80mm or 120mm with grill</t>
         </is>
       </c>
       <c r="O57" s="21" t="inlineStr">
         <is>
-          <t>Permanent soldering of boards, diodes, and aviation plugs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="34" customHeight="1">
-      <c r="A58" s="27" t="inlineStr">
-        <is>
-          <t>Subtotal — Category E (Connectors &amp; Wiring):</t>
-        </is>
-      </c>
-      <c r="B58" s="28" t="n"/>
-      <c r="C58" s="28" t="n"/>
-      <c r="D58" s="28" t="n"/>
-      <c r="E58" s="28" t="n"/>
-      <c r="F58" s="28" t="n"/>
-      <c r="G58" s="28" t="n"/>
-      <c r="H58" s="28" t="n"/>
-      <c r="I58" s="28" t="n"/>
-      <c r="J58" s="29">
-        <f>SUM(J48:J57)</f>
-        <v/>
-      </c>
-      <c r="K58" s="29">
-        <f>SUM(K48:K57)</f>
-        <v/>
-      </c>
-      <c r="L58" s="29">
-        <f>SUM(L48:L57)</f>
-        <v/>
-      </c>
-      <c r="M58" s="28" t="n"/>
-      <c r="N58" s="28" t="n"/>
-      <c r="O58" s="28" t="n"/>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>🌀 CATEGORY F: ACTUATORS (THE THINGS BEING CONTROLLED)</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="8" t="n"/>
-      <c r="L59" s="8" t="n"/>
-      <c r="M59" s="8" t="n"/>
-      <c r="N59" s="8" t="n"/>
-      <c r="O59" s="8" t="n"/>
+          <t>Draws in fresh filtered air &amp; circulates humidity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="44" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>12V DC High-Pressure Misting Pump (60W)</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>Actuators</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>Self-priming diaphragm pump, 4-5 L/min, 0.8 MPa (115 PSI), auto pressure switch.</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>350</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="J58" s="16">
+        <f>F58*H58</f>
+        <v/>
+      </c>
+      <c r="K58" s="16">
+        <f>F58*I58</f>
+        <v/>
+      </c>
+      <c r="L58" s="16" t="n"/>
+      <c r="M58" s="12" t="inlineStr">
+        <is>
+          <t>Shopee / Lazada</t>
+        </is>
+      </c>
+      <c r="N58" s="17" t="inlineStr">
+        <is>
+          <t>12V diaphragm pump misting 60W high pressure</t>
+        </is>
+      </c>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>Atomizes water into ultra-fine fog without wetting beds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>Brass Misting Nozzles (0.3mm Orifice)</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>Actuators</t>
+        </is>
+      </c>
+      <c r="E59" s="21" t="inlineStr">
+        <is>
+          <t>Solid brass with stainless orifice, anti-drip spring, 20-70 bar rating.</t>
+        </is>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H59" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I59" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="J59" s="25">
+        <f>F59*H59</f>
+        <v/>
+      </c>
+      <c r="K59" s="25">
+        <f>F59*I59</f>
+        <v/>
+      </c>
+      <c r="L59" s="25" t="n"/>
+      <c r="M59" s="21" t="inlineStr">
+        <is>
+          <t>Shopee / Lazada / Hardware</t>
+        </is>
+      </c>
+      <c r="N59" s="26" t="inlineStr">
+        <is>
+          <t>0.3mm brass misting nozzle anti drip</t>
+        </is>
+      </c>
+      <c r="O59" s="21" t="inlineStr">
+        <is>
+          <t>Overhead spray nozzles creating 15-30 micron fog.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="44" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
@@ -4015,12 +4015,12 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>12V DC Exhaust Fan (120mm / 4-Inch)</t>
+          <t>Misting Tubing Kit (6mm PE Tubing 5m + Tees)</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>120×120×25mm, 12V DC, ball bearing, moisture-resistant, &gt;70 CFM.</t>
+          <t>5m 1/4" (6mm) PE tubing + 5 slip-lock tee fittings + 1 end plug.</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
@@ -4038,14 +4038,14 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>kit</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="J60" s="16">
         <f>F60*H60</f>
@@ -4063,12 +4063,12 @@
       </c>
       <c r="N60" s="17" t="inlineStr">
         <is>
-          <t>12V 120mm cooling fan ball bearing high airflow</t>
+          <t>Misting system kit 6mm PE pipe slip lock fittings</t>
         </is>
       </c>
       <c r="O60" s="12" t="inlineStr">
         <is>
-          <t>Extracts stale CO2 and heat from grow room ceiling.</t>
+          <t>Overhead pipe manifold connecting pump to brass nozzles.</t>
         </is>
       </c>
     </row>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F6</t>
         </is>
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>12V DC Circulation / Intake Fan (80-120mm)</t>
+          <t>12V DC Solenoid Valve (1/2" NC)</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="E61" s="21" t="inlineStr">
         <is>
-          <t>12V DC, brushless, 0.2A, low noise with finger protection grill.</t>
+          <t>Direct-acting 12V DC valve, normally closed (NC), brass or nylon body.</t>
         </is>
       </c>
       <c r="F61" s="22" t="n">
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="H61" s="24" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="I61" s="24" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="J61" s="25">
         <f>F61*H61</f>
@@ -4123,17 +4123,17 @@
       <c r="L61" s="25" t="n"/>
       <c r="M61" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Lazada</t>
+          <t>Shopee / Lazada / Makerlab PH</t>
         </is>
       </c>
       <c r="N61" s="26" t="inlineStr">
         <is>
-          <t>12V DC brushless fan 80mm or 120mm with grill</t>
+          <t>12V DC electric solenoid valve 1/2 inch normally closed</t>
         </is>
       </c>
       <c r="O61" s="21" t="inlineStr">
         <is>
-          <t>Draws in fresh filtered air &amp; circulates humidity.</t>
+          <t>Primary water shutoff. Shuts closed if power fails.</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>12V DC High-Pressure Misting Pump (60W)</t>
+          <t>Push-Fit Water Fittings (1/2" Male to 6mm)</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
@@ -4160,22 +4160,22 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Self-priming diaphragm pump, 4-5 L/min, 0.8 MPa (115 PSI), auto pressure switch.</t>
+          <t>Food-grade POM push-fit adapter, 1/2" BSP thread to 1/4" (6mm) OD tube.</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="J62" s="16">
         <f>F62*H62</f>
@@ -4188,17 +4188,17 @@
       <c r="L62" s="16" t="n"/>
       <c r="M62" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Lazada</t>
+          <t>Hardware Store / Shopee</t>
         </is>
       </c>
       <c r="N62" s="17" t="inlineStr">
         <is>
-          <t>12V diaphragm pump misting 60W high pressure</t>
+          <t>Quick connect fitting 1/2 male thread to 1/4 6mm tube</t>
         </is>
       </c>
       <c r="O62" s="12" t="inlineStr">
         <is>
-          <t>Atomizes water into ultra-fine fog without wetting beds.</t>
+          <t>Leak-free transition from solenoid/pump to PE misting tube.</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>Brass Misting Nozzles (0.3mm Orifice)</t>
+          <t>12V Full-Spectrum LED Grow Light Strip (1m)</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -4225,22 +4225,22 @@
       </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
-          <t>Solid brass with stainless orifice, anti-drip spring, 20-70 bar rating.</t>
+          <t>12V SMD5050, 4:1 Red:Blue + White spectrum, IP65 waterproof silicone jacket.</t>
         </is>
       </c>
       <c r="F63" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>strip</t>
         </is>
       </c>
       <c r="H63" s="24" t="n">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="I63" s="24" t="n">
-        <v>30</v>
+        <v>800</v>
       </c>
       <c r="J63" s="25">
         <f>F63*H63</f>
@@ -4253,17 +4253,17 @@
       <c r="L63" s="25" t="n"/>
       <c r="M63" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Lazada / Hardware</t>
+          <t>Shopee / Lazada</t>
         </is>
       </c>
       <c r="N63" s="26" t="inlineStr">
         <is>
-          <t>0.3mm brass misting nozzle anti drip</t>
+          <t>12V full spectrum LED grow light strip waterproof IP65</t>
         </is>
       </c>
       <c r="O63" s="21" t="inlineStr">
         <is>
-          <t>Overhead spray nozzles creating 15-30 micron fog.</t>
+          <t>Stimulates oyster mushroom pinhead &amp; cap formation.</t>
         </is>
       </c>
     </row>
@@ -4275,12 +4275,12 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Misting Tubing Kit (6mm PE Tubing 5m + Tees)</t>
+          <t>Water Reservoir Container (5-10 Liters)</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>5m 1/4" (6mm) PE tubing + 5 slip-lock tee fittings + 1 end plug.</t>
+          <t>Heavy-duty translucent HDPE plastic container with tight lid &amp; drain port.</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
@@ -4298,14 +4298,14 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>kit</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="J64" s="16">
         <f>F64*H64</f>
@@ -4318,17 +4318,17 @@
       <c r="L64" s="16" t="n"/>
       <c r="M64" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Lazada</t>
+          <t>Hardware Store / Grocery</t>
         </is>
       </c>
       <c r="N64" s="17" t="inlineStr">
         <is>
-          <t>Misting system kit 6mm PE pipe slip lock fittings</t>
+          <t>Plastic container with lid 10L translucent</t>
         </is>
       </c>
       <c r="O64" s="12" t="inlineStr">
         <is>
-          <t>Overhead pipe manifold connecting pump to brass nozzles.</t>
+          <t>Dedicated clean water supply; holds capacitive level sensor.</t>
         </is>
       </c>
     </row>
@@ -4340,12 +4340,12 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>12V DC Solenoid Valve (1/2" NC)</t>
+          <t>PTFE Thread Seal Teflon Tape (1/2" × 10m)</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="E65" s="21" t="inlineStr">
         <is>
-          <t>Direct-acting 12V DC valve, normally closed (NC), brass or nylon body.</t>
+          <t>Standard density PTFE sealant tape for plumbing connections.</t>
         </is>
       </c>
       <c r="F65" s="22" t="n">
@@ -4363,14 +4363,14 @@
       </c>
       <c r="G65" s="23" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="H65" s="24" t="n">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="I65" s="24" t="n">
-        <v>450</v>
+        <v>30</v>
       </c>
       <c r="J65" s="25">
         <f>F65*H65</f>
@@ -4383,17 +4383,17 @@
       <c r="L65" s="25" t="n"/>
       <c r="M65" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Lazada / Makerlab PH</t>
+          <t>Any Hardware Store</t>
         </is>
       </c>
       <c r="N65" s="26" t="inlineStr">
         <is>
-          <t>12V DC electric solenoid valve 1/2 inch normally closed</t>
+          <t>Teflon tape 1/2 inch</t>
         </is>
       </c>
       <c r="O65" s="21" t="inlineStr">
         <is>
-          <t>Primary water shutoff. Shuts closed if power fails.</t>
+          <t>Guarantees zero leaks on all threaded water joints.</t>
         </is>
       </c>
     </row>
@@ -4405,12 +4405,12 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Push-Fit Water Fittings (1/2" Male to 6mm)</t>
+          <t>Stainless Hose Clamps (10-16mm, SS304)</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Food-grade POM push-fit adapter, 1/2" BSP thread to 1/4" (6mm) OD tube.</t>
+          <t>304 stainless steel band &amp; screw, rustproof in 95% humidity.</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="H66" s="15" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="J66" s="16">
         <f>F66*H66</f>
@@ -4448,17 +4448,17 @@
       <c r="L66" s="16" t="n"/>
       <c r="M66" s="12" t="inlineStr">
         <is>
-          <t>Hardware Store / Shopee</t>
+          <t>Hardware Store</t>
         </is>
       </c>
       <c r="N66" s="17" t="inlineStr">
         <is>
-          <t>Quick connect fitting 1/2 male thread to 1/4 6mm tube</t>
+          <t>Stainless hose clamps 10-16mm</t>
         </is>
       </c>
       <c r="O66" s="12" t="inlineStr">
         <is>
-          <t>Leak-free transition from solenoid/pump to PE misting tube.</t>
+          <t>Secures intake/discharge hoses to pump barbs under pressure.</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F12</t>
         </is>
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>12V Full-Spectrum LED Grow Light Strip (1m)</t>
+          <t>6mm Inline One-Way Check Valve</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E67" s="21" t="inlineStr">
         <is>
-          <t>12V SMD5050, 4:1 Red:Blue + White spectrum, IP65 waterproof silicone jacket.</t>
+          <t>Diaphragm non-return valve, cracking pressure 0.01 MPa, fits 6mm tube.</t>
         </is>
       </c>
       <c r="F67" s="22" t="n">
@@ -4493,14 +4493,14 @@
       </c>
       <c r="G67" s="23" t="inlineStr">
         <is>
-          <t>strip</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H67" s="24" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="I67" s="24" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
       <c r="J67" s="25">
         <f>F67*H67</f>
@@ -4513,149 +4513,70 @@
       <c r="L67" s="25" t="n"/>
       <c r="M67" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Lazada</t>
+          <t>Shopee / Aquarium Store</t>
         </is>
       </c>
       <c r="N67" s="26" t="inlineStr">
         <is>
-          <t>12V full spectrum LED grow light strip waterproof IP65</t>
+          <t>Inline one way check valve 6mm</t>
         </is>
       </c>
       <c r="O67" s="21" t="inlineStr">
         <is>
-          <t>Stimulates oyster mushroom pinhead &amp; cap formation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="44" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>F9</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>Water Reservoir Container (5-10 Liters)</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>Actuators</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>Heavy-duty translucent HDPE plastic container with tight lid &amp; drain port.</t>
-        </is>
-      </c>
-      <c r="F68" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="I68" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="J68" s="16">
-        <f>F68*H68</f>
-        <v/>
-      </c>
-      <c r="K68" s="16">
-        <f>F68*I68</f>
-        <v/>
-      </c>
-      <c r="L68" s="16" t="n"/>
-      <c r="M68" s="12" t="inlineStr">
-        <is>
-          <t>Hardware Store / Grocery</t>
-        </is>
-      </c>
-      <c r="N68" s="17" t="inlineStr">
-        <is>
-          <t>Plastic container with lid 10L translucent</t>
-        </is>
-      </c>
-      <c r="O68" s="12" t="inlineStr">
-        <is>
-          <t>Dedicated clean water supply; holds capacitive level sensor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="44" customHeight="1">
-      <c r="A69" s="18" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B69" s="18" t="inlineStr">
-        <is>
-          <t>F10</t>
-        </is>
-      </c>
-      <c r="C69" s="19" t="inlineStr">
-        <is>
-          <t>PTFE Thread Seal Teflon Tape (1/2" × 10m)</t>
-        </is>
-      </c>
-      <c r="D69" s="20" t="inlineStr">
-        <is>
-          <t>Actuators</t>
-        </is>
-      </c>
-      <c r="E69" s="21" t="inlineStr">
-        <is>
-          <t>Standard density PTFE sealant tape for plumbing connections.</t>
-        </is>
-      </c>
-      <c r="F69" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="23" t="inlineStr">
-        <is>
-          <t>roll</t>
-        </is>
-      </c>
-      <c r="H69" s="24" t="n">
-        <v>25</v>
-      </c>
-      <c r="I69" s="24" t="n">
-        <v>30</v>
-      </c>
-      <c r="J69" s="25">
-        <f>F69*H69</f>
-        <v/>
-      </c>
-      <c r="K69" s="25">
-        <f>F69*I69</f>
-        <v/>
-      </c>
-      <c r="L69" s="25" t="n"/>
-      <c r="M69" s="21" t="inlineStr">
-        <is>
-          <t>Any Hardware Store</t>
-        </is>
-      </c>
-      <c r="N69" s="26" t="inlineStr">
-        <is>
-          <t>Teflon tape 1/2 inch</t>
-        </is>
-      </c>
-      <c r="O69" s="21" t="inlineStr">
-        <is>
-          <t>Guarantees zero leaks on all threaded water joints.</t>
-        </is>
-      </c>
+          <t>Prevents backflow and keeps pump head primed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>Subtotal — Category F (Actuators):</t>
+        </is>
+      </c>
+      <c r="B68" s="28" t="n"/>
+      <c r="C68" s="28" t="n"/>
+      <c r="D68" s="28" t="n"/>
+      <c r="E68" s="28" t="n"/>
+      <c r="F68" s="28" t="n"/>
+      <c r="G68" s="28" t="n"/>
+      <c r="H68" s="28" t="n"/>
+      <c r="I68" s="28" t="n"/>
+      <c r="J68" s="29">
+        <f>SUM(J56:J67)</f>
+        <v/>
+      </c>
+      <c r="K68" s="29">
+        <f>SUM(K56:K67)</f>
+        <v/>
+      </c>
+      <c r="L68" s="29">
+        <f>SUM(L56:L67)</f>
+        <v/>
+      </c>
+      <c r="M68" s="28" t="n"/>
+      <c r="N68" s="28" t="n"/>
+      <c r="O68" s="28" t="n"/>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>📦 CATEGORY G: ENCLOSURE &amp; MOUNTING</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="8" t="n"/>
+      <c r="O69" s="8" t="n"/>
     </row>
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4665,37 +4586,37 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Stainless Hose Clamps (10-16mm, SS304)</t>
+          <t>IP65 ABS Waterproof Enclosure (255×200×80mm)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Actuators</t>
+          <t>Enclosure &amp; Mounting</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>304 stainless steel band &amp; screw, rustproof in 95% humidity.</t>
+          <t>Weatherproof ABS box with rubber silicone sealing gasket &amp; brass inserts.</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="J70" s="16">
         <f>F70*H70</f>
@@ -4708,17 +4629,17 @@
       <c r="L70" s="16" t="n"/>
       <c r="M70" s="12" t="inlineStr">
         <is>
-          <t>Hardware Store</t>
+          <t>Shopee / Lazada / Hardware</t>
         </is>
       </c>
       <c r="N70" s="17" t="inlineStr">
         <is>
-          <t>Stainless hose clamps 10-16mm</t>
+          <t>IP65 waterproof junction box ABS 255x200x80</t>
         </is>
       </c>
       <c r="O70" s="12" t="inlineStr">
         <is>
-          <t>Secures intake/discharge hoses to pump barbs under pressure.</t>
+          <t>Houses ESP32, PSU, relays, and terminal blocks safely.</t>
         </is>
       </c>
     </row>
@@ -4730,22 +4651,22 @@
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>F12</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>6mm Inline One-Way Check Valve</t>
+          <t>35mm DIN Rail (15cm) + Mounting Clips</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>Actuators</t>
+          <t>Enclosure &amp; Mounting</t>
         </is>
       </c>
       <c r="E71" s="21" t="inlineStr">
         <is>
-          <t>Diaphragm non-return valve, cracking pressure 0.01 MPa, fits 6mm tube.</t>
+          <t>Standard slotted steel DIN rail 35mm + modular mounting clips &amp; brackets.</t>
         </is>
       </c>
       <c r="F71" s="22" t="n">
@@ -4753,14 +4674,14 @@
       </c>
       <c r="G71" s="23" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>set</t>
         </is>
       </c>
       <c r="H71" s="24" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I71" s="24" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J71" s="25">
         <f>F71*H71</f>
@@ -4773,70 +4694,149 @@
       <c r="L71" s="25" t="n"/>
       <c r="M71" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Aquarium Store</t>
+          <t>Shopee / Lazada</t>
         </is>
       </c>
       <c r="N71" s="26" t="inlineStr">
         <is>
-          <t>Inline one way check valve 6mm</t>
+          <t>DIN rail 35mm 15cm with mounting brackets</t>
         </is>
       </c>
       <c r="O71" s="21" t="inlineStr">
         <is>
-          <t>Prevents backflow and keeps pump head primed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="34" customHeight="1">
-      <c r="A72" s="27" t="inlineStr">
-        <is>
-          <t>Subtotal — Category F (Actuators):</t>
-        </is>
-      </c>
-      <c r="B72" s="28" t="n"/>
-      <c r="C72" s="28" t="n"/>
-      <c r="D72" s="28" t="n"/>
-      <c r="E72" s="28" t="n"/>
-      <c r="F72" s="28" t="n"/>
-      <c r="G72" s="28" t="n"/>
-      <c r="H72" s="28" t="n"/>
-      <c r="I72" s="28" t="n"/>
-      <c r="J72" s="29">
-        <f>SUM(J60:J71)</f>
-        <v/>
-      </c>
-      <c r="K72" s="29">
-        <f>SUM(K60:K71)</f>
-        <v/>
-      </c>
-      <c r="L72" s="29">
-        <f>SUM(L60:L71)</f>
-        <v/>
-      </c>
-      <c r="M72" s="28" t="n"/>
-      <c r="N72" s="28" t="n"/>
-      <c r="O72" s="28" t="n"/>
-    </row>
-    <row r="73" ht="34" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>📦 CATEGORY G: ENCLOSURE &amp; MOUNTING</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
-      <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="8" t="n"/>
-      <c r="J73" s="8" t="n"/>
-      <c r="K73" s="8" t="n"/>
-      <c r="L73" s="8" t="n"/>
-      <c r="M73" s="8" t="n"/>
-      <c r="N73" s="8" t="n"/>
-      <c r="O73" s="8" t="n"/>
+          <t>Clean industrial mounting for terminal blocks and PSU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>M3 Nylon PCB Standoffs / Spacers Kit</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Enclosure &amp; Mounting</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>Assorted M3 nylon threaded pillars (6-20mm), nuts, and screws.</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J72" s="16">
+        <f>F72*H72</f>
+        <v/>
+      </c>
+      <c r="K72" s="16">
+        <f>F72*I72</f>
+        <v/>
+      </c>
+      <c r="L72" s="16" t="n"/>
+      <c r="M72" s="12" t="inlineStr">
+        <is>
+          <t>Shopee / Electronics Store</t>
+        </is>
+      </c>
+      <c r="N72" s="17" t="inlineStr">
+        <is>
+          <t>M3 nylon hex standoff assortment kit</t>
+        </is>
+      </c>
+      <c r="O72" s="12" t="inlineStr">
+        <is>
+          <t>Mounts ESP32 board and perfboards elevated off base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="44" customHeight="1">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>Wall-Mount Brackets + Screws (Stainless)</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>Enclosure &amp; Mounting</t>
+        </is>
+      </c>
+      <c r="E73" s="21" t="inlineStr">
+        <is>
+          <t>304 stainless steel L-brackets with masonry wall plugs &amp; screws.</t>
+        </is>
+      </c>
+      <c r="F73" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="H73" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J73" s="25">
+        <f>F73*H73</f>
+        <v/>
+      </c>
+      <c r="K73" s="25">
+        <f>F73*I73</f>
+        <v/>
+      </c>
+      <c r="L73" s="25" t="n"/>
+      <c r="M73" s="21" t="inlineStr">
+        <is>
+          <t>Hardware Store</t>
+        </is>
+      </c>
+      <c r="N73" s="26" t="inlineStr">
+        <is>
+          <t>Stainless steel mounting bracket with screws</t>
+        </is>
+      </c>
+      <c r="O73" s="21" t="inlineStr">
+        <is>
+          <t>Secures controller cabinet firmly to mushroom house wall.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="44" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>IP65 ABS Waterproof Enclosure (255×200×80mm)</t>
+          <t>Rubber Wiring Grommets Assortment</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Weatherproof ABS box with rubber silicone sealing gasket &amp; brass inserts.</t>
+          <t>Weatherproof nitrile rubber grommets (10mm to 25mm).</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
@@ -4869,14 +4869,14 @@
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="H74" s="15" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="J74" s="16">
         <f>F74*H74</f>
@@ -4889,330 +4889,330 @@
       <c r="L74" s="16" t="n"/>
       <c r="M74" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Lazada / Hardware</t>
+          <t>Shopee / Hardware Store</t>
         </is>
       </c>
       <c r="N74" s="17" t="inlineStr">
         <is>
-          <t>IP65 waterproof junction box ABS 255x200x80</t>
+          <t>Rubber grommets assortment kit</t>
         </is>
       </c>
       <c r="O74" s="12" t="inlineStr">
         <is>
-          <t>Houses ESP32, PSU, relays, and terminal blocks safely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="44" customHeight="1">
-      <c r="A75" s="18" t="inlineStr">
+          <t>Protects wiring where cables pass through drilled holes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>Subtotal — Category G (Enclosure &amp; Mounting):</t>
+        </is>
+      </c>
+      <c r="B75" s="28" t="n"/>
+      <c r="C75" s="28" t="n"/>
+      <c r="D75" s="28" t="n"/>
+      <c r="E75" s="28" t="n"/>
+      <c r="F75" s="28" t="n"/>
+      <c r="G75" s="28" t="n"/>
+      <c r="H75" s="28" t="n"/>
+      <c r="I75" s="28" t="n"/>
+      <c r="J75" s="29">
+        <f>SUM(J70:J74)</f>
+        <v/>
+      </c>
+      <c r="K75" s="29">
+        <f>SUM(K70:K74)</f>
+        <v/>
+      </c>
+      <c r="L75" s="29">
+        <f>SUM(L70:L74)</f>
+        <v/>
+      </c>
+      <c r="M75" s="28" t="n"/>
+      <c r="N75" s="28" t="n"/>
+      <c r="O75" s="28" t="n"/>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>🔧 CATEGORY H: MISCELLANEOUS, TOOLS &amp; FABRICATION CONSUMABLES</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="8" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+      <c r="L76" s="8" t="n"/>
+      <c r="M76" s="8" t="n"/>
+      <c r="N76" s="8" t="n"/>
+      <c r="O76" s="8" t="n"/>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>To Buy</t>
         </is>
       </c>
-      <c r="B75" s="18" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="inlineStr">
-        <is>
-          <t>35mm DIN Rail (15cm) + Mounting Clips</t>
-        </is>
-      </c>
-      <c r="D75" s="20" t="inlineStr">
-        <is>
-          <t>Enclosure &amp; Mounting</t>
-        </is>
-      </c>
-      <c r="E75" s="21" t="inlineStr">
-        <is>
-          <t>Standard slotted steel DIN rail 35mm + modular mounting clips &amp; brackets.</t>
-        </is>
-      </c>
-      <c r="F75" s="22" t="n">
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>USB-C Data &amp; Sync Cable (1.0m, Fast Sync)</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Miscellaneous, Tools &amp; Fabrication Consumables</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>28/24 AWG shielded copper cable supporting high-speed serial data (not charge-only).</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="23" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="H75" s="24" t="n">
-        <v>60</v>
-      </c>
-      <c r="I75" s="24" t="n">
-        <v>120</v>
-      </c>
-      <c r="J75" s="25">
-        <f>F75*H75</f>
-        <v/>
-      </c>
-      <c r="K75" s="25">
-        <f>F75*I75</f>
-        <v/>
-      </c>
-      <c r="L75" s="25" t="n"/>
-      <c r="M75" s="21" t="inlineStr">
-        <is>
-          <t>Shopee / Lazada</t>
-        </is>
-      </c>
-      <c r="N75" s="26" t="inlineStr">
-        <is>
-          <t>DIN rail 35mm 15cm with mounting brackets</t>
-        </is>
-      </c>
-      <c r="O75" s="21" t="inlineStr">
-        <is>
-          <t>Clean industrial mounting for terminal blocks and PSU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="44" customHeight="1">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J77" s="16">
+        <f>F77*H77</f>
+        <v/>
+      </c>
+      <c r="K77" s="16">
+        <f>F77*I77</f>
+        <v/>
+      </c>
+      <c r="L77" s="16" t="n"/>
+      <c r="M77" s="12" t="inlineStr">
+        <is>
+          <t>Shopee / Phone Accessories Store</t>
+        </is>
+      </c>
+      <c r="N77" s="17" t="inlineStr">
+        <is>
+          <t>USB-C data cable 1m high speed</t>
+        </is>
+      </c>
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>Required for flashing firmware and Serial Monitor logs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="44" customHeight="1">
+      <c r="A78" s="18" t="inlineStr">
         <is>
           <t>To Buy</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>M3 Nylon PCB Standoffs / Spacers Kit</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>Enclosure &amp; Mounting</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>Assorted M3 nylon threaded pillars (6-20mm), nuts, and screws.</t>
-        </is>
-      </c>
-      <c r="F76" s="13" t="n">
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>4–20mm Titanium HSS Step Drill Bit</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>Miscellaneous, Tools &amp; Fabrication Consumables</t>
+        </is>
+      </c>
+      <c r="E78" s="21" t="inlineStr">
+        <is>
+          <t>High-speed steel conical step bit with 9 increment steps (4-20mm).</t>
+        </is>
+      </c>
+      <c r="F78" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="14" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="H76" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="I76" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="J76" s="16">
-        <f>F76*H76</f>
-        <v/>
-      </c>
-      <c r="K76" s="16">
-        <f>F76*I76</f>
-        <v/>
-      </c>
-      <c r="L76" s="16" t="n"/>
-      <c r="M76" s="12" t="inlineStr">
-        <is>
-          <t>Shopee / Electronics Store</t>
-        </is>
-      </c>
-      <c r="N76" s="17" t="inlineStr">
-        <is>
-          <t>M3 nylon hex standoff assortment kit</t>
-        </is>
-      </c>
-      <c r="O76" s="12" t="inlineStr">
-        <is>
-          <t>Mounts ESP32 board and perfboards elevated off base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="44" customHeight="1">
-      <c r="A77" s="18" t="inlineStr">
+      <c r="G78" s="23" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="H78" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="I78" s="24" t="n">
+        <v>200</v>
+      </c>
+      <c r="J78" s="25">
+        <f>F78*H78</f>
+        <v/>
+      </c>
+      <c r="K78" s="25">
+        <f>F78*I78</f>
+        <v/>
+      </c>
+      <c r="L78" s="25" t="n"/>
+      <c r="M78" s="21" t="inlineStr">
+        <is>
+          <t>Shopee / Hardware Store</t>
+        </is>
+      </c>
+      <c r="N78" s="26" t="inlineStr">
+        <is>
+          <t>Step drill bit 4-20mm titanium HSS</t>
+        </is>
+      </c>
+      <c r="O78" s="21" t="inlineStr">
+        <is>
+          <t>Cuts clean 16mm holes for GX16 sockets, glands &amp; switches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>To Buy</t>
         </is>
       </c>
-      <c r="B77" s="18" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="C77" s="19" t="inlineStr">
-        <is>
-          <t>Wall-Mount Brackets + Screws (Stainless)</t>
-        </is>
-      </c>
-      <c r="D77" s="20" t="inlineStr">
-        <is>
-          <t>Enclosure &amp; Mounting</t>
-        </is>
-      </c>
-      <c r="E77" s="21" t="inlineStr">
-        <is>
-          <t>304 stainless steel L-brackets with masonry wall plugs &amp; screws.</t>
-        </is>
-      </c>
-      <c r="F77" s="22" t="n">
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Electrical Tape (3M Scotch or equivalent)</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Miscellaneous, Tools &amp; Fabrication Consumables</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Heavy-duty vinyl electrical insulating tape, flame retardant.</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>rolls</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="J79" s="16">
+        <f>F79*H79</f>
+        <v/>
+      </c>
+      <c r="K79" s="16">
+        <f>F79*I79</f>
+        <v/>
+      </c>
+      <c r="L79" s="16" t="n"/>
+      <c r="M79" s="12" t="inlineStr">
+        <is>
+          <t>Any Hardware Store</t>
+        </is>
+      </c>
+      <c r="N79" s="17" t="inlineStr">
+        <is>
+          <t>3M electrical tape original black</t>
+        </is>
+      </c>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>General wire insulation, color identification, and bundling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="44" customHeight="1">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>To Buy</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>3M VHB Double-Sided Foam Tape (12mm × 3m)</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>Miscellaneous, Tools &amp; Fabrication Consumables</t>
+        </is>
+      </c>
+      <c r="E80" s="21" t="inlineStr">
+        <is>
+          <t>High-strength acrylic foam bonding tape, extreme moisture resistance.</t>
+        </is>
+      </c>
+      <c r="F80" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="G77" s="23" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="H77" s="24" t="n">
-        <v>30</v>
-      </c>
-      <c r="I77" s="24" t="n">
-        <v>60</v>
-      </c>
-      <c r="J77" s="25">
-        <f>F77*H77</f>
-        <v/>
-      </c>
-      <c r="K77" s="25">
-        <f>F77*I77</f>
-        <v/>
-      </c>
-      <c r="L77" s="25" t="n"/>
-      <c r="M77" s="21" t="inlineStr">
-        <is>
-          <t>Hardware Store</t>
-        </is>
-      </c>
-      <c r="N77" s="26" t="inlineStr">
-        <is>
-          <t>Stainless steel mounting bracket with screws</t>
-        </is>
-      </c>
-      <c r="O77" s="21" t="inlineStr">
-        <is>
-          <t>Secures controller cabinet firmly to mushroom house wall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="44" customHeight="1">
-      <c r="A78" s="9" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>G5</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>Rubber Wiring Grommets Assortment</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>Enclosure &amp; Mounting</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>Weatherproof nitrile rubber grommets (10mm to 25mm).</t>
-        </is>
-      </c>
-      <c r="F78" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="14" t="inlineStr">
-        <is>
-          <t>pack</t>
-        </is>
-      </c>
-      <c r="H78" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="I78" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="J78" s="16">
-        <f>F78*H78</f>
-        <v/>
-      </c>
-      <c r="K78" s="16">
-        <f>F78*I78</f>
-        <v/>
-      </c>
-      <c r="L78" s="16" t="n"/>
-      <c r="M78" s="12" t="inlineStr">
+      <c r="G80" s="23" t="inlineStr">
+        <is>
+          <t>roll</t>
+        </is>
+      </c>
+      <c r="H80" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="I80" s="24" t="n">
+        <v>80</v>
+      </c>
+      <c r="J80" s="25">
+        <f>F80*H80</f>
+        <v/>
+      </c>
+      <c r="K80" s="25">
+        <f>F80*I80</f>
+        <v/>
+      </c>
+      <c r="L80" s="25" t="n"/>
+      <c r="M80" s="21" t="inlineStr">
         <is>
           <t>Shopee / Hardware Store</t>
         </is>
       </c>
-      <c r="N78" s="17" t="inlineStr">
-        <is>
-          <t>Rubber grommets assortment kit</t>
-        </is>
-      </c>
-      <c r="O78" s="12" t="inlineStr">
-        <is>
-          <t>Protects wiring where cables pass through drilled holes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="34" customHeight="1">
-      <c r="A79" s="27" t="inlineStr">
-        <is>
-          <t>Subtotal — Category G (Enclosure &amp; Mounting):</t>
-        </is>
-      </c>
-      <c r="B79" s="28" t="n"/>
-      <c r="C79" s="28" t="n"/>
-      <c r="D79" s="28" t="n"/>
-      <c r="E79" s="28" t="n"/>
-      <c r="F79" s="28" t="n"/>
-      <c r="G79" s="28" t="n"/>
-      <c r="H79" s="28" t="n"/>
-      <c r="I79" s="28" t="n"/>
-      <c r="J79" s="29">
-        <f>SUM(J74:J78)</f>
-        <v/>
-      </c>
-      <c r="K79" s="29">
-        <f>SUM(K74:K78)</f>
-        <v/>
-      </c>
-      <c r="L79" s="29">
-        <f>SUM(L74:L78)</f>
-        <v/>
-      </c>
-      <c r="M79" s="28" t="n"/>
-      <c r="N79" s="28" t="n"/>
-      <c r="O79" s="28" t="n"/>
-    </row>
-    <row r="80" ht="34" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>🔧 CATEGORY H: MISCELLANEOUS, TOOLS &amp; FABRICATION CONSUMABLES</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="8" t="n"/>
-      <c r="F80" s="8" t="n"/>
-      <c r="G80" s="8" t="n"/>
-      <c r="H80" s="8" t="n"/>
-      <c r="I80" s="8" t="n"/>
-      <c r="J80" s="8" t="n"/>
-      <c r="K80" s="8" t="n"/>
-      <c r="L80" s="8" t="n"/>
-      <c r="M80" s="8" t="n"/>
-      <c r="N80" s="8" t="n"/>
-      <c r="O80" s="8" t="n"/>
+      <c r="N80" s="26" t="inlineStr">
+        <is>
+          <t>3M VHB double sided tape heavy duty</t>
+        </is>
+      </c>
+      <c r="O80" s="21" t="inlineStr">
+        <is>
+          <t>Mounts OLED display and indicator bezels to cabinet face.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="44" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>USB-C Data &amp; Sync Cable (1.0m, Fast Sync)</t>
+          <t>Clear Weatherproof Silicone Sealant (100ml)</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>28/24 AWG shielded copper cable supporting high-speed serial data (not charge-only).</t>
+          <t>100% RTV silicone sealant, mold-resistant, flexible waterproof seal.</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
@@ -5245,14 +5245,14 @@
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>tube</t>
         </is>
       </c>
       <c r="H81" s="15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J81" s="16">
         <f>F81*H81</f>
@@ -5265,17 +5265,17 @@
       <c r="L81" s="16" t="n"/>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>Shopee / Phone Accessories Store</t>
+          <t>Any Hardware Store</t>
         </is>
       </c>
       <c r="N81" s="17" t="inlineStr">
         <is>
-          <t>USB-C data cable 1m high speed</t>
+          <t>Clear silicone sealant RTV waterproof</t>
         </is>
       </c>
       <c r="O81" s="12" t="inlineStr">
         <is>
-          <t>Required for flashing firmware and Serial Monitor logs.</t>
+          <t>Seals perimeter of all cutouts to keep enclosure IP65.</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="B82" s="18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H6</t>
         </is>
       </c>
       <c r="C82" s="19" t="inlineStr">
         <is>
-          <t>4–20mm Titanium HSS Step Drill Bit</t>
+          <t>Printable Weatherproof Vinyl Label Sheets</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="E82" s="21" t="inlineStr">
         <is>
-          <t>High-speed steel conical step bit with 9 increment steps (4-20mm).</t>
+          <t>Waterproof adhesive vinyl sticker paper for labeling ports &amp; switches.</t>
         </is>
       </c>
       <c r="F82" s="22" t="n">
@@ -5310,14 +5310,14 @@
       </c>
       <c r="G82" s="23" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>set</t>
         </is>
       </c>
       <c r="H82" s="24" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I82" s="24" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J82" s="25">
         <f>F82*H82</f>
@@ -5330,17 +5330,17 @@
       <c r="L82" s="25" t="n"/>
       <c r="M82" s="21" t="inlineStr">
         <is>
-          <t>Shopee / Hardware Store</t>
+          <t>Shopee / Print Shop</t>
         </is>
       </c>
       <c r="N82" s="26" t="inlineStr">
         <is>
-          <t>Step drill bit 4-20mm titanium HSS</t>
+          <t>Waterproof label sticker paper A4 vinyl</t>
         </is>
       </c>
       <c r="O82" s="21" t="inlineStr">
         <is>
-          <t>Cuts clean 16mm holes for GX16 sockets, glands &amp; switches.</t>
+          <t>Clear labeling: [MAINS], [EXHAUST], [MISTER], [LIGHT], [PROBE].</t>
         </is>
       </c>
     </row>
@@ -5352,12 +5352,12 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Electrical Tape (3M Scotch or equivalent)</t>
+          <t>40W Soldering Iron with Stand &amp; Sponge</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -5367,22 +5367,22 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Heavy-duty vinyl electrical insulating tape, flame retardant.</t>
+          <t>220V 40W pencil iron with fine tip, wire stand &amp; cleaning sponge.</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>rolls</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="H83" s="15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>40</v>
+        <v>350</v>
       </c>
       <c r="J83" s="16">
         <f>F83*H83</f>
@@ -5395,366 +5395,106 @@
       <c r="L83" s="16" t="n"/>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>Any Hardware Store</t>
+          <t>Shopee / Hardware Store (0 if owned)</t>
         </is>
       </c>
       <c r="N83" s="17" t="inlineStr">
         <is>
-          <t>3M electrical tape original black</t>
+          <t>Soldering iron 40W with stand</t>
         </is>
       </c>
       <c r="O83" s="12" t="inlineStr">
         <is>
-          <t>General wire insulation, color identification, and bundling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="44" customHeight="1">
-      <c r="A84" s="18" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B84" s="18" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C84" s="19" t="inlineStr">
-        <is>
-          <t>3M VHB Double-Sided Foam Tape (12mm × 3m)</t>
-        </is>
-      </c>
-      <c r="D84" s="20" t="inlineStr">
-        <is>
-          <t>Miscellaneous, Tools &amp; Fabrication Consumables</t>
-        </is>
-      </c>
-      <c r="E84" s="21" t="inlineStr">
-        <is>
-          <t>High-strength acrylic foam bonding tape, extreme moisture resistance.</t>
-        </is>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="23" t="inlineStr">
-        <is>
-          <t>roll</t>
-        </is>
-      </c>
-      <c r="H84" s="24" t="n">
-        <v>40</v>
-      </c>
-      <c r="I84" s="24" t="n">
-        <v>80</v>
-      </c>
-      <c r="J84" s="25">
-        <f>F84*H84</f>
-        <v/>
-      </c>
-      <c r="K84" s="25">
-        <f>F84*I84</f>
-        <v/>
-      </c>
-      <c r="L84" s="25" t="n"/>
-      <c r="M84" s="21" t="inlineStr">
-        <is>
-          <t>Shopee / Hardware Store</t>
-        </is>
-      </c>
-      <c r="N84" s="26" t="inlineStr">
-        <is>
-          <t>3M VHB double sided tape heavy duty</t>
-        </is>
-      </c>
-      <c r="O84" s="21" t="inlineStr">
-        <is>
-          <t>Mounts OLED display and indicator bezels to cabinet face.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="44" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>Clear Weatherproof Silicone Sealant (100ml)</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>Miscellaneous, Tools &amp; Fabrication Consumables</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>100% RTV silicone sealant, mold-resistant, flexible waterproof seal.</t>
-        </is>
-      </c>
-      <c r="F85" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>tube</t>
-        </is>
-      </c>
-      <c r="H85" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="I85" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="J85" s="16">
-        <f>F85*H85</f>
-        <v/>
-      </c>
-      <c r="K85" s="16">
-        <f>F85*I85</f>
-        <v/>
-      </c>
-      <c r="L85" s="16" t="n"/>
-      <c r="M85" s="12" t="inlineStr">
-        <is>
-          <t>Any Hardware Store</t>
-        </is>
-      </c>
-      <c r="N85" s="17" t="inlineStr">
-        <is>
-          <t>Clear silicone sealant RTV waterproof</t>
-        </is>
-      </c>
-      <c r="O85" s="12" t="inlineStr">
-        <is>
-          <t>Seals perimeter of all cutouts to keep enclosure IP65.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="44" customHeight="1">
-      <c r="A86" s="18" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B86" s="18" t="inlineStr">
-        <is>
-          <t>H6</t>
-        </is>
-      </c>
-      <c r="C86" s="19" t="inlineStr">
-        <is>
-          <t>Printable Weatherproof Vinyl Label Sheets</t>
-        </is>
-      </c>
-      <c r="D86" s="20" t="inlineStr">
-        <is>
-          <t>Miscellaneous, Tools &amp; Fabrication Consumables</t>
-        </is>
-      </c>
-      <c r="E86" s="21" t="inlineStr">
-        <is>
-          <t>Waterproof adhesive vinyl sticker paper for labeling ports &amp; switches.</t>
-        </is>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="23" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="H86" s="24" t="n">
-        <v>30</v>
-      </c>
-      <c r="I86" s="24" t="n">
-        <v>50</v>
-      </c>
-      <c r="J86" s="25">
-        <f>F86*H86</f>
-        <v/>
-      </c>
-      <c r="K86" s="25">
-        <f>F86*I86</f>
-        <v/>
-      </c>
-      <c r="L86" s="25" t="n"/>
-      <c r="M86" s="21" t="inlineStr">
-        <is>
-          <t>Shopee / Print Shop</t>
-        </is>
-      </c>
-      <c r="N86" s="26" t="inlineStr">
-        <is>
-          <t>Waterproof label sticker paper A4 vinyl</t>
-        </is>
-      </c>
-      <c r="O86" s="21" t="inlineStr">
-        <is>
-          <t>Clear labeling: [MAINS], [EXHAUST], [MISTER], [LIGHT], [PROBE].</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="44" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>To Buy</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>40W Soldering Iron with Stand &amp; Sponge</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>Miscellaneous, Tools &amp; Fabrication Consumables</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>220V 40W pencil iron with fine tip, wire stand &amp; cleaning sponge.</t>
-        </is>
-      </c>
-      <c r="F87" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="H87" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="15" t="n">
-        <v>350</v>
-      </c>
-      <c r="J87" s="16">
-        <f>F87*H87</f>
-        <v/>
-      </c>
-      <c r="K87" s="16">
-        <f>F87*I87</f>
-        <v/>
-      </c>
-      <c r="L87" s="16" t="n"/>
-      <c r="M87" s="12" t="inlineStr">
-        <is>
-          <t>Shopee / Hardware Store (0 if owned)</t>
-        </is>
-      </c>
-      <c r="N87" s="17" t="inlineStr">
-        <is>
-          <t>Soldering iron 40W with stand</t>
-        </is>
-      </c>
-      <c r="O87" s="12" t="inlineStr">
-        <is>
           <t>Essential for perfboard, diodes, and GX16 connectors.</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="34" customHeight="1">
-      <c r="A88" s="27" t="inlineStr">
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
         <is>
           <t>Subtotal — Category H (Miscellaneous, Tools &amp; Fabrication Consumables):</t>
         </is>
       </c>
-      <c r="B88" s="28" t="n"/>
-      <c r="C88" s="28" t="n"/>
-      <c r="D88" s="28" t="n"/>
-      <c r="E88" s="28" t="n"/>
-      <c r="F88" s="28" t="n"/>
-      <c r="G88" s="28" t="n"/>
-      <c r="H88" s="28" t="n"/>
-      <c r="I88" s="28" t="n"/>
-      <c r="J88" s="29">
-        <f>SUM(J81:J87)</f>
-        <v/>
-      </c>
-      <c r="K88" s="29">
-        <f>SUM(K81:K87)</f>
-        <v/>
-      </c>
-      <c r="L88" s="29">
-        <f>SUM(L81:L87)</f>
-        <v/>
-      </c>
-      <c r="M88" s="28" t="n"/>
-      <c r="N88" s="28" t="n"/>
-      <c r="O88" s="28" t="n"/>
-    </row>
-    <row r="89" ht="16" customHeight="1"/>
-    <row r="90" ht="40" customHeight="1">
-      <c r="A90" s="30" t="inlineStr">
+      <c r="B84" s="28" t="n"/>
+      <c r="C84" s="28" t="n"/>
+      <c r="D84" s="28" t="n"/>
+      <c r="E84" s="28" t="n"/>
+      <c r="F84" s="28" t="n"/>
+      <c r="G84" s="28" t="n"/>
+      <c r="H84" s="28" t="n"/>
+      <c r="I84" s="28" t="n"/>
+      <c r="J84" s="29">
+        <f>SUM(J77:J83)</f>
+        <v/>
+      </c>
+      <c r="K84" s="29">
+        <f>SUM(K77:K83)</f>
+        <v/>
+      </c>
+      <c r="L84" s="29">
+        <f>SUM(L77:L83)</f>
+        <v/>
+      </c>
+      <c r="M84" s="28" t="n"/>
+      <c r="N84" s="28" t="n"/>
+      <c r="O84" s="28" t="n"/>
+    </row>
+    <row r="85" ht="16" customHeight="1"/>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" s="30" t="inlineStr">
         <is>
           <t>★ GRAND TOTAL (ALL 68 COMPONENTS):</t>
         </is>
       </c>
-      <c r="B90" s="31" t="n"/>
-      <c r="C90" s="31" t="n"/>
-      <c r="D90" s="31" t="n"/>
-      <c r="E90" s="31" t="n"/>
-      <c r="F90" s="31" t="n"/>
-      <c r="G90" s="31" t="n"/>
-      <c r="H90" s="31" t="n"/>
-      <c r="I90" s="31" t="n"/>
-      <c r="J90" s="32">
-        <f>J13+J23+J37+J46+J58+J72+J79+J88</f>
-        <v/>
-      </c>
-      <c r="K90" s="32">
-        <f>K13+K23+K37+K46+K58+K72+K79+K88</f>
-        <v/>
-      </c>
-      <c r="L90" s="32">
-        <f>L13+L23+L37+L46+L58+L72+L79+L88</f>
-        <v/>
-      </c>
-      <c r="M90" s="31" t="n"/>
-      <c r="N90" s="31" t="n"/>
-      <c r="O90" s="31" t="n"/>
+      <c r="B86" s="31" t="n"/>
+      <c r="C86" s="31" t="n"/>
+      <c r="D86" s="31" t="n"/>
+      <c r="E86" s="31" t="n"/>
+      <c r="F86" s="31" t="n"/>
+      <c r="G86" s="31" t="n"/>
+      <c r="H86" s="31" t="n"/>
+      <c r="I86" s="31" t="n"/>
+      <c r="J86" s="32">
+        <f>J13+J19+J33+J42+J54+J68+J75+J84</f>
+        <v/>
+      </c>
+      <c r="K86" s="32">
+        <f>K13+K19+K33+K42+K54+K68+K75+K84</f>
+        <v/>
+      </c>
+      <c r="L86" s="32">
+        <f>L13+L19+L33+L42+L54+L68+L75+L84</f>
+        <v/>
+      </c>
+      <c r="M86" s="31" t="n"/>
+      <c r="N86" s="31" t="n"/>
+      <c r="O86" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A80:O80"/>
+    <mergeCell ref="A69:O69"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A84:I84"/>
     <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A86:I86"/>
+    <mergeCell ref="A55:O55"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A76:O76"/>
     <mergeCell ref="A14:O14"/>
-    <mergeCell ref="A47:O47"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A43:O43"/>
+    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A58:I58"/>
-    <mergeCell ref="A59:O59"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A73:O73"/>
-    <mergeCell ref="A88:I88"/>
+    <mergeCell ref="A34:O34"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A15 A16 A17 A18 A19 A20 A21 A22 A25 A26 A27 A28 A29 A30 A31 A32 A33 A34 A35 A36 A39 A40 A41 A42 A43 A44 A45 A48 A49 A50 A51 A52 A53 A54 A55 A56 A57 A60 A61 A62 A63 A64 A65 A66 A67 A68 A69 A70 A71 A74 A75 A76 A77 A78 A81 A82 A83 A84 A85 A86 A87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid status from the list" promptTitle="Status" prompt="Select procurement status" type="list">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A15 A16 A17 A18 A21 A22 A23 A24 A25 A26 A27 A28 A29 A30 A31 A32 A35 A36 A37 A38 A39 A40 A41 A44 A45 A46 A47 A48 A49 A50 A51 A52 A53 A56 A57 A58 A59 A60 A61 A62 A63 A64 A65 A66 A67 A70 A71 A72 A73 A74 A77 A78 A79 A80 A81 A82 A83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid status from the list" promptTitle="Status" prompt="Select procurement status" type="list">
       <formula1>"To Buy,Ordered,Received,In Stock,Not Needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5833,15 +5573,15 @@
       </c>
       <c r="B5" s="34" t="n"/>
       <c r="C5" s="36">
-        <f>'📋 Materials Checklist'!J90</f>
+        <f>'📋 Materials Checklist'!J86</f>
         <v/>
       </c>
       <c r="D5" s="36">
-        <f>'📋 Materials Checklist'!K90</f>
+        <f>'📋 Materials Checklist'!K86</f>
         <v/>
       </c>
       <c r="E5" s="36">
-        <f>'📋 Materials Checklist'!L90</f>
+        <f>'📋 Materials Checklist'!L86</f>
         <v/>
       </c>
       <c r="F5" s="37">
@@ -5968,22 +5708,22 @@
       </c>
       <c r="B11" s="44" t="inlineStr">
         <is>
-          <t>Hanging Sensor Probe Housing (PVC Bell Reducer Design)</t>
+          <t>Hanging Sensor Probe Housing (Mini Radiation Shield Design)</t>
         </is>
       </c>
       <c r="C11" s="22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D11" s="24">
-        <f>'📋 Materials Checklist'!J23</f>
+        <f>'📋 Materials Checklist'!J19</f>
         <v/>
       </c>
       <c r="E11" s="24">
-        <f>'📋 Materials Checklist'!K23</f>
+        <f>'📋 Materials Checklist'!K19</f>
         <v/>
       </c>
       <c r="F11" s="25">
-        <f>'📋 Materials Checklist'!L23</f>
+        <f>'📋 Materials Checklist'!L19</f>
         <v/>
       </c>
       <c r="G11" s="45">
@@ -6006,15 +5746,15 @@
         <v>12</v>
       </c>
       <c r="D12" s="15">
-        <f>'📋 Materials Checklist'!J37</f>
+        <f>'📋 Materials Checklist'!J33</f>
         <v/>
       </c>
       <c r="E12" s="15">
-        <f>'📋 Materials Checklist'!K37</f>
+        <f>'📋 Materials Checklist'!K33</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>'📋 Materials Checklist'!L37</f>
+        <f>'📋 Materials Checklist'!L33</f>
         <v/>
       </c>
       <c r="G12" s="43">
@@ -6037,15 +5777,15 @@
         <v>7</v>
       </c>
       <c r="D13" s="24">
-        <f>'📋 Materials Checklist'!J46</f>
+        <f>'📋 Materials Checklist'!J42</f>
         <v/>
       </c>
       <c r="E13" s="24">
-        <f>'📋 Materials Checklist'!K46</f>
+        <f>'📋 Materials Checklist'!K42</f>
         <v/>
       </c>
       <c r="F13" s="25">
-        <f>'📋 Materials Checklist'!L46</f>
+        <f>'📋 Materials Checklist'!L42</f>
         <v/>
       </c>
       <c r="G13" s="45">
@@ -6068,15 +5808,15 @@
         <v>10</v>
       </c>
       <c r="D14" s="15">
-        <f>'📋 Materials Checklist'!J58</f>
+        <f>'📋 Materials Checklist'!J54</f>
         <v/>
       </c>
       <c r="E14" s="15">
-        <f>'📋 Materials Checklist'!K58</f>
+        <f>'📋 Materials Checklist'!K54</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>'📋 Materials Checklist'!L58</f>
+        <f>'📋 Materials Checklist'!L54</f>
         <v/>
       </c>
       <c r="G14" s="43">
@@ -6099,15 +5839,15 @@
         <v>12</v>
       </c>
       <c r="D15" s="24">
-        <f>'📋 Materials Checklist'!J72</f>
+        <f>'📋 Materials Checklist'!J68</f>
         <v/>
       </c>
       <c r="E15" s="24">
-        <f>'📋 Materials Checklist'!K72</f>
+        <f>'📋 Materials Checklist'!K68</f>
         <v/>
       </c>
       <c r="F15" s="25">
-        <f>'📋 Materials Checklist'!L72</f>
+        <f>'📋 Materials Checklist'!L68</f>
         <v/>
       </c>
       <c r="G15" s="45">
@@ -6130,15 +5870,15 @@
         <v>5</v>
       </c>
       <c r="D16" s="15">
-        <f>'📋 Materials Checklist'!J79</f>
+        <f>'📋 Materials Checklist'!J75</f>
         <v/>
       </c>
       <c r="E16" s="15">
-        <f>'📋 Materials Checklist'!K79</f>
+        <f>'📋 Materials Checklist'!K75</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>'📋 Materials Checklist'!L79</f>
+        <f>'📋 Materials Checklist'!L75</f>
         <v/>
       </c>
       <c r="G16" s="43">
@@ -6161,15 +5901,15 @@
         <v>7</v>
       </c>
       <c r="D17" s="24">
-        <f>'📋 Materials Checklist'!J88</f>
+        <f>'📋 Materials Checklist'!J84</f>
         <v/>
       </c>
       <c r="E17" s="24">
-        <f>'📋 Materials Checklist'!K88</f>
+        <f>'📋 Materials Checklist'!K84</f>
         <v/>
       </c>
       <c r="F17" s="25">
-        <f>'📋 Materials Checklist'!L88</f>
+        <f>'📋 Materials Checklist'!L84</f>
         <v/>
       </c>
       <c r="G17" s="45">
